--- a/research/traditional_assets/database/data/united_states/united_states_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.037</v>
+        <v>0.02245</v>
       </c>
       <c r="E2">
-        <v>0.11245</v>
+        <v>0.007904999999999999</v>
       </c>
       <c r="F2">
-        <v>0.134</v>
+        <v>0.0491</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0003873100204255792</v>
+        <v>0.0009943950271997593</v>
       </c>
       <c r="J2">
-        <v>-0.000320933812244676</v>
+        <v>0.0008058376520526061</v>
       </c>
       <c r="K2">
-        <v>130223.88</v>
+        <v>102625.92</v>
       </c>
       <c r="L2">
-        <v>0.3260588961700364</v>
+        <v>0.2696192235666501</v>
       </c>
       <c r="M2">
-        <v>76866.65700000001</v>
+        <v>62862.116</v>
       </c>
       <c r="N2">
-        <v>0.06266875582475043</v>
+        <v>0.06475538872682274</v>
       </c>
       <c r="O2">
-        <v>0.5902654490098129</v>
+        <v>0.6125364430350539</v>
       </c>
       <c r="P2">
-        <v>25650.657</v>
+        <v>29107.116</v>
       </c>
       <c r="Q2">
-        <v>0.0209127705433765</v>
+        <v>0.02998376019185739</v>
       </c>
       <c r="R2">
-        <v>0.1969735274359818</v>
+        <v>0.2836234354829657</v>
       </c>
       <c r="S2">
-        <v>51216</v>
+        <v>33755</v>
       </c>
       <c r="T2">
-        <v>0.6662967013122477</v>
+        <v>0.5369688796349139</v>
       </c>
       <c r="U2">
-        <v>1717420.2</v>
+        <v>1360855.5</v>
       </c>
       <c r="V2">
-        <v>1.400198621390469</v>
+        <v>1.401841562309718</v>
       </c>
       <c r="W2">
-        <v>0.1361126956382504</v>
+        <v>0.1023941369513455</v>
       </c>
       <c r="X2">
-        <v>0.06141438347640225</v>
+        <v>0.0958177452565805</v>
       </c>
       <c r="Y2">
-        <v>0.07469831216184815</v>
+        <v>0.006576391694764996</v>
       </c>
       <c r="Z2">
-        <v>0.2715968923842905</v>
+        <v>0.3175608716755457</v>
       </c>
       <c r="AA2">
-        <v>0.0001925569717345524</v>
+        <v>0.0009048476687635754</v>
       </c>
       <c r="AB2">
-        <v>0.03809683315649962</v>
+        <v>0.06233580827874149</v>
       </c>
       <c r="AC2">
-        <v>-0.03833342886049498</v>
+        <v>-0.06168891080681541</v>
       </c>
       <c r="AD2">
-        <v>2061368.6</v>
+        <v>2075375.2</v>
       </c>
       <c r="AE2">
-        <v>28817.25409756861</v>
+        <v>25501.3281824544</v>
       </c>
       <c r="AF2">
-        <v>2090185.854097569</v>
+        <v>2100876.528182454</v>
       </c>
       <c r="AG2">
-        <v>372765.6540975687</v>
+        <v>740021.0281824544</v>
       </c>
       <c r="AH2">
-        <v>0.6301927509872036</v>
+        <v>0.6839594015165582</v>
       </c>
       <c r="AI2">
-        <v>0.6742842021128295</v>
+        <v>0.6812159212677307</v>
       </c>
       <c r="AJ2">
-        <v>0.2330775401829393</v>
+        <v>0.4325625828629178</v>
       </c>
       <c r="AK2">
-        <v>0.2696435411384699</v>
+        <v>0.4294572221564941</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>367.5263569656345</v>
+        <v>378.8034712202476</v>
       </c>
       <c r="AP2">
-        <v>66.46128346594165</v>
+        <v>135.0707738299515</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.11</v>
+        <v>0.027</v>
       </c>
       <c r="E3">
-        <v>0.289</v>
+        <v>-0.00953</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,16 +731,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.004063398081192853</v>
+        <v>0.01069618415444151</v>
       </c>
       <c r="J3">
-        <v>0.003024548194397322</v>
+        <v>0.008078813465397058</v>
       </c>
       <c r="K3">
-        <v>7.88</v>
+        <v>3.92</v>
       </c>
       <c r="L3">
-        <v>0.1849765258215962</v>
+        <v>0.1232704402515723</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>69.2</v>
+        <v>36.5</v>
       </c>
       <c r="V3">
-        <v>1.320610687022901</v>
+        <v>0.8314350797266515</v>
       </c>
       <c r="W3">
-        <v>0.1409660107334526</v>
+        <v>0.05467224546722455</v>
       </c>
       <c r="X3">
-        <v>0.05110712745141262</v>
+        <v>0.08263048010607527</v>
       </c>
       <c r="Y3">
-        <v>0.08985888328203999</v>
+        <v>-0.02795823463885072</v>
       </c>
       <c r="Z3">
-        <v>0.3232427562553037</v>
+        <v>0.415902072125919</v>
       </c>
       <c r="AA3">
-        <v>0.0009776632947839925</v>
+        <v>0.003359995260577412</v>
       </c>
       <c r="AB3">
-        <v>0.03688578352198881</v>
+        <v>0.06034905012138189</v>
       </c>
       <c r="AC3">
-        <v>-0.03590812022720482</v>
+        <v>-0.05698905486080447</v>
       </c>
       <c r="AD3">
-        <v>34.6</v>
+        <v>37.2</v>
       </c>
       <c r="AE3">
-        <v>2.954496208705923</v>
+        <v>2.124306719443799</v>
       </c>
       <c r="AF3">
-        <v>37.55449620870593</v>
+        <v>39.3243067194438</v>
       </c>
       <c r="AG3">
-        <v>-31.64550379129408</v>
+        <v>2.824306719443804</v>
       </c>
       <c r="AH3">
-        <v>0.4174832586641883</v>
+        <v>0.4725098744530174</v>
       </c>
       <c r="AI3">
-        <v>0.2562493623888902</v>
+        <v>0.3108043643079736</v>
       </c>
       <c r="AJ3">
-        <v>-1.524754129084554</v>
+        <v>0.0604461985150975</v>
       </c>
       <c r="AK3">
-        <v>-0.4090971480948318</v>
+        <v>0.03137271279684067</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>45.28795811518324</v>
+        <v>48.62745098039216</v>
       </c>
       <c r="AP3">
-        <v>-41.42081648075141</v>
+        <v>3.691904208423273</v>
       </c>
     </row>
     <row r="4">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0409</v>
+        <v>0.0279</v>
       </c>
       <c r="E4">
-        <v>0.0582</v>
+        <v>0.0179</v>
       </c>
       <c r="F4">
-        <v>0.134</v>
+        <v>0.0491</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,91 +859,91 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.001784154724556626</v>
+        <v>0.002776566643425367</v>
       </c>
       <c r="J4">
-        <v>0.001404512996555181</v>
+        <v>0.002193411048770477</v>
       </c>
       <c r="K4">
-        <v>7809</v>
+        <v>6573</v>
       </c>
       <c r="L4">
-        <v>0.3338463511607028</v>
+        <v>0.2904294803817604</v>
       </c>
       <c r="M4">
-        <v>4078</v>
+        <v>2818</v>
       </c>
       <c r="N4">
-        <v>0.04896222416726399</v>
+        <v>0.04222741365333062</v>
       </c>
       <c r="O4">
-        <v>0.5222179536432322</v>
+        <v>0.4287235661037578</v>
       </c>
       <c r="P4">
-        <v>2529</v>
+        <v>2745</v>
       </c>
       <c r="Q4">
-        <v>0.030364263099316</v>
+        <v>0.04113351684825853</v>
       </c>
       <c r="R4">
-        <v>0.323857087975413</v>
+        <v>0.4176175262437243</v>
       </c>
       <c r="S4">
-        <v>1549</v>
+        <v>73</v>
       </c>
       <c r="T4">
-        <v>0.3798430603236881</v>
+        <v>0.02590489709013485</v>
       </c>
       <c r="U4">
-        <v>63904</v>
+        <v>41652</v>
       </c>
       <c r="V4">
-        <v>0.7672589438903477</v>
+        <v>0.6241505441761983</v>
       </c>
       <c r="W4">
-        <v>0.1676434597797385</v>
+        <v>0.1375824175824176</v>
       </c>
       <c r="X4">
-        <v>0.04998689169748595</v>
+        <v>0.08422350121924385</v>
       </c>
       <c r="Y4">
-        <v>0.1176565680822526</v>
+        <v>0.05335891636317372</v>
       </c>
       <c r="Z4">
-        <v>0.4093534099956681</v>
+        <v>0.6663760797694516</v>
       </c>
       <c r="AA4">
-        <v>0.0005749421845230973</v>
+        <v>0.001461636656002672</v>
       </c>
       <c r="AB4">
-        <v>0.03758125374649246</v>
+        <v>0.06154373930059193</v>
       </c>
       <c r="AC4">
-        <v>-0.03700631156196936</v>
+        <v>-0.06008210264458926</v>
       </c>
       <c r="AD4">
-        <v>53044</v>
+        <v>64109</v>
       </c>
       <c r="AE4">
-        <v>1241.33418418948</v>
+        <v>1075.803718629985</v>
       </c>
       <c r="AF4">
-        <v>54285.33418418948</v>
+        <v>65184.80371862998</v>
       </c>
       <c r="AG4">
-        <v>-9618.66581581052</v>
+        <v>23532.80371862998</v>
       </c>
       <c r="AH4">
-        <v>0.3945899711824264</v>
+        <v>0.4941285949690876</v>
       </c>
       <c r="AI4">
-        <v>0.4995736104707894</v>
+        <v>0.5760267647725187</v>
       </c>
       <c r="AJ4">
-        <v>-0.1305641557293428</v>
+        <v>0.2607030361049186</v>
       </c>
       <c r="AK4">
-        <v>-0.2148974284610373</v>
+        <v>0.3290803975749362</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -952,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>182.9103448275862</v>
+        <v>230.6079136690647</v>
       </c>
       <c r="AP4">
-        <v>-33.16781315796731</v>
+        <v>84.65037308859706</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Citigroup Inc. (NYSE:C)</t>
+          <t>Wells Fargo &amp; Company (NYSE:WFC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0331</v>
+        <v>-0.0251</v>
       </c>
       <c r="E5">
-        <v>0.0949</v>
+        <v>-0.0549</v>
       </c>
       <c r="F5">
-        <v>0.212</v>
+        <v>0.104</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,91 +990,91 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.002243563484153805</v>
+        <v>0.001970894381311234</v>
       </c>
       <c r="J5">
-        <v>0.001794540902863907</v>
+        <v>0.001594970557487413</v>
       </c>
       <c r="K5">
-        <v>23088</v>
+        <v>16068</v>
       </c>
       <c r="L5">
-        <v>0.3062922033988246</v>
+        <v>0.2138977635782748</v>
       </c>
       <c r="M5">
-        <v>11826.972</v>
+        <v>16898</v>
       </c>
       <c r="N5">
-        <v>0.09869800442126715</v>
+        <v>0.1074012681205477</v>
       </c>
       <c r="O5">
-        <v>0.512256237006237</v>
+        <v>1.051655464276823</v>
       </c>
       <c r="P5">
-        <v>4047.972</v>
+        <v>3859</v>
       </c>
       <c r="Q5">
-        <v>0.03378098454559338</v>
+        <v>0.02452725137159389</v>
       </c>
       <c r="R5">
-        <v>0.1753279625779626</v>
+        <v>0.2401667911376649</v>
       </c>
       <c r="S5">
-        <v>7779</v>
+        <v>13039</v>
       </c>
       <c r="T5">
-        <v>0.6577338645935747</v>
+        <v>0.7716297786720322</v>
       </c>
       <c r="U5">
-        <v>307175</v>
+        <v>220249</v>
       </c>
       <c r="V5">
-        <v>2.563425322060688</v>
+        <v>1.399871103224199</v>
       </c>
       <c r="W5">
-        <v>0.1312593805430482</v>
+        <v>0.09472213543355361</v>
       </c>
       <c r="X5">
-        <v>0.1198295985225956</v>
+        <v>0.09403531487532535</v>
       </c>
       <c r="Y5">
-        <v>0.0114297820204526</v>
+        <v>0.0006868205582282599</v>
       </c>
       <c r="Z5">
-        <v>0.1705760694503598</v>
+        <v>1.463593347231619</v>
       </c>
       <c r="AA5">
-        <v>0.0003061057336784251</v>
+        <v>0.002334388296968885</v>
       </c>
       <c r="AB5">
-        <v>0.03854181001682662</v>
+        <v>0.0634200198115509</v>
       </c>
       <c r="AC5">
-        <v>-0.03823570428314819</v>
+        <v>-0.06108563151458202</v>
       </c>
       <c r="AD5">
-        <v>559976</v>
+        <v>228194</v>
       </c>
       <c r="AE5">
-        <v>3109.412140639852</v>
+        <v>3999.7320703795</v>
       </c>
       <c r="AF5">
-        <v>563085.4121406398</v>
+        <v>232193.7320703795</v>
       </c>
       <c r="AG5">
-        <v>255910.4121406398</v>
+        <v>11944.73207037951</v>
       </c>
       <c r="AH5">
-        <v>0.8245318301263653</v>
+        <v>0.5960885391394422</v>
       </c>
       <c r="AI5">
-        <v>0.7363525440336751</v>
+        <v>0.5654948541126128</v>
       </c>
       <c r="AJ5">
-        <v>0.681083194621003</v>
+        <v>0.07056200888250233</v>
       </c>
       <c r="AK5">
-        <v>0.5593420650748454</v>
+        <v>0.06275018588006032</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1083,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>707.9342604298356</v>
+        <v>240.710970464135</v>
       </c>
       <c r="AP5">
-        <v>323.5277018212893</v>
+        <v>12.59992834428219</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co. (NYSE:JPM)</t>
+          <t>Bank of America Corporation (NYSE:BAC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0809</v>
+        <v>0.0179</v>
       </c>
       <c r="E6">
-        <v>0.164</v>
+        <v>0.06</v>
       </c>
       <c r="F6">
-        <v>0.153</v>
+        <v>0.0707</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1121,91 +1121,91 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-0.001248850763269198</v>
+        <v>-0.0004744055934391601</v>
       </c>
       <c r="J6">
-        <v>-0.001013915434106529</v>
+        <v>-0.0004209447365028792</v>
       </c>
       <c r="K6">
-        <v>50071</v>
+        <v>27409</v>
       </c>
       <c r="L6">
-        <v>0.3817085442458986</v>
+        <v>0.2994995410638577</v>
       </c>
       <c r="M6">
-        <v>27220.61</v>
+        <v>18427.04</v>
       </c>
       <c r="N6">
-        <v>0.05816787273616225</v>
+        <v>0.06935202086540235</v>
       </c>
       <c r="O6">
-        <v>0.5436402308721615</v>
+        <v>0.6722988799299501</v>
       </c>
       <c r="P6">
-        <v>10934.61</v>
+        <v>6819.04</v>
       </c>
       <c r="Q6">
-        <v>0.02336622885745643</v>
+        <v>0.02566414379965601</v>
       </c>
       <c r="R6">
-        <v>0.2183820974216613</v>
+        <v>0.2487883541902295</v>
       </c>
       <c r="S6">
-        <v>16286</v>
+        <v>11608</v>
       </c>
       <c r="T6">
-        <v>0.5982966583041306</v>
+        <v>0.6299438216881279</v>
       </c>
       <c r="U6">
-        <v>738569</v>
+        <v>198376</v>
       </c>
       <c r="V6">
-        <v>1.578252199303198</v>
+        <v>0.746608054858244</v>
       </c>
       <c r="W6">
-        <v>0.2077203899605891</v>
+        <v>0.1100661384691374</v>
       </c>
       <c r="X6">
-        <v>0.06398730373015575</v>
+        <v>0.1073701606033377</v>
       </c>
       <c r="Y6">
-        <v>0.1437330862304333</v>
+        <v>0.002695977865799656</v>
       </c>
       <c r="Z6">
-        <v>0.3222387140226373</v>
+        <v>0.1854258181968228</v>
       </c>
       <c r="AA6">
-        <v>-0.000326722805614192</v>
+        <v>-7.805402218169235e-05</v>
       </c>
       <c r="AB6">
-        <v>0.03810443063222758</v>
+        <v>0.06221413607686709</v>
       </c>
       <c r="AC6">
-        <v>-0.03843115343784178</v>
+        <v>-0.06229219009904879</v>
       </c>
       <c r="AD6">
-        <v>675820</v>
+        <v>562513</v>
       </c>
       <c r="AE6">
-        <v>8849.096238613001</v>
+        <v>9802.07851144589</v>
       </c>
       <c r="AF6">
-        <v>684669.096238613</v>
+        <v>572315.0785114459</v>
       </c>
       <c r="AG6">
-        <v>-53899.90376138699</v>
+        <v>373939.0785114459</v>
       </c>
       <c r="AH6">
-        <v>0.5940031332306602</v>
+        <v>0.6829388209954101</v>
       </c>
       <c r="AI6">
-        <v>0.7024335737166748</v>
+        <v>0.6798390489586479</v>
       </c>
       <c r="AJ6">
-        <v>-0.1301720961512574</v>
+        <v>0.5846067528603882</v>
       </c>
       <c r="AK6">
-        <v>-0.2282529581675307</v>
+        <v>0.5811352523543343</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1214,10 +1214,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>420.8094645080947</v>
+        <v>293.434011476265</v>
       </c>
       <c r="AP6">
-        <v>-33.56158391119987</v>
+        <v>195.0647253580834</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company (NYSE:WFC)</t>
+          <t>Citigroup Inc. (NYSE:C)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,13 +1237,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0155</v>
+        <v>0.0179</v>
       </c>
       <c r="E7">
-        <v>-0.0329</v>
+        <v>-0.00209</v>
       </c>
       <c r="F7">
-        <v>0.127</v>
+        <v>-0.116</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1252,91 +1252,91 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.0001476929360924995</v>
+        <v>0.002650732251117159</v>
       </c>
       <c r="J7">
-        <v>0.0001307833730720186</v>
+        <v>0.00213997116723661</v>
       </c>
       <c r="K7">
-        <v>18813</v>
+        <v>15505</v>
       </c>
       <c r="L7">
-        <v>0.2405908306157683</v>
+        <v>0.2191581387459716</v>
       </c>
       <c r="M7">
-        <v>9747</v>
+        <v>7702.276</v>
       </c>
       <c r="N7">
-        <v>0.05094941439797938</v>
+        <v>0.0879216107958664</v>
       </c>
       <c r="O7">
-        <v>0.5180991867325785</v>
+        <v>0.4967607868429539</v>
       </c>
       <c r="P7">
-        <v>2001</v>
+        <v>3951.276</v>
       </c>
       <c r="Q7">
-        <v>0.01045960584901577</v>
+        <v>0.04510388236140173</v>
       </c>
       <c r="R7">
-        <v>0.1063626215914527</v>
+        <v>0.2548388261851016</v>
       </c>
       <c r="S7">
-        <v>7746</v>
+        <v>3751</v>
       </c>
       <c r="T7">
-        <v>0.7947060634041243</v>
+        <v>0.4869989078552884</v>
       </c>
       <c r="U7">
-        <v>333449</v>
+        <v>283441</v>
       </c>
       <c r="V7">
-        <v>1.743001054846807</v>
+        <v>3.235483808369263</v>
       </c>
       <c r="W7">
-        <v>0.1168872320596459</v>
+        <v>0.0847823709536308</v>
       </c>
       <c r="X7">
-        <v>0.05884146322264876</v>
+        <v>0.195050704520092</v>
       </c>
       <c r="Y7">
-        <v>0.05804576883699709</v>
+        <v>-0.1102683335664612</v>
       </c>
       <c r="Z7">
-        <v>0.6041150945630699</v>
+        <v>0.1626464350797467</v>
       </c>
       <c r="AA7">
-        <v>7.900820979067976e-05</v>
+        <v>0.000348058681524479</v>
       </c>
       <c r="AB7">
-        <v>0.0386104545023684</v>
+        <v>0.06268975595117486</v>
       </c>
       <c r="AC7">
-        <v>-0.03853144629257772</v>
+        <v>-0.06234169726965038</v>
       </c>
       <c r="AD7">
-        <v>217938</v>
+        <v>576462</v>
       </c>
       <c r="AE7">
-        <v>4912.255754311235</v>
+        <v>2877.329973489816</v>
       </c>
       <c r="AF7">
-        <v>222850.2557543112</v>
+        <v>579339.3299734899</v>
       </c>
       <c r="AG7">
-        <v>-110598.7442456888</v>
+        <v>295898.3299734899</v>
       </c>
       <c r="AH7">
-        <v>0.5380807348555007</v>
+        <v>0.8686486404495295</v>
       </c>
       <c r="AI7">
-        <v>0.5383880452048763</v>
+        <v>0.7442155811016645</v>
       </c>
       <c r="AJ7">
-        <v>-1.370345512659351</v>
+        <v>0.7715687337566309</v>
       </c>
       <c r="AK7">
-        <v>-1.374371119698151</v>
+        <v>0.5977558917000337</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>219.2535211267606</v>
+        <v>755.5203145478375</v>
       </c>
       <c r="AP7">
-        <v>-111.2663422994857</v>
+        <v>387.8090825340627</v>
       </c>
     </row>
     <row r="8">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bank of America Corporation (NYSE:BAC)</t>
+          <t>JPMorgan Chase &amp; Co. (NYSE:JPM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1368,13 +1368,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0274</v>
+        <v>0.0508</v>
       </c>
       <c r="E8">
-        <v>0.13</v>
+        <v>0.0659</v>
       </c>
       <c r="F8">
-        <v>0.07000000000000001</v>
+        <v>-0.008489999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1383,91 +1383,91 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-0.002340251049529278</v>
+        <v>0.0001919648351125582</v>
       </c>
       <c r="J8">
-        <v>-0.002206696430660334</v>
+        <v>0.0001560909170165664</v>
       </c>
       <c r="K8">
-        <v>30435</v>
+        <v>37067</v>
       </c>
       <c r="L8">
-        <v>0.3337024691899478</v>
+        <v>0.3073931251814073</v>
       </c>
       <c r="M8">
-        <v>23994.075</v>
+        <v>17016.8</v>
       </c>
       <c r="N8">
-        <v>0.06589789236711223</v>
+        <v>0.043262009626209</v>
       </c>
       <c r="O8">
-        <v>0.788371118777723</v>
+        <v>0.4590822024981789</v>
       </c>
       <c r="P8">
-        <v>6138.075000000001</v>
+        <v>11732.8</v>
       </c>
       <c r="Q8">
-        <v>0.01685775366173784</v>
+        <v>0.02982843463767482</v>
       </c>
       <c r="R8">
-        <v>0.2016781665845244</v>
+        <v>0.3165295276121617</v>
       </c>
       <c r="S8">
-        <v>17856</v>
+        <v>5284</v>
       </c>
       <c r="T8">
-        <v>0.7441837203559628</v>
+        <v>0.3105166658831273</v>
       </c>
       <c r="U8">
-        <v>274254</v>
+        <v>617101</v>
       </c>
       <c r="V8">
-        <v>0.753217641157244</v>
+        <v>1.568863088379907</v>
       </c>
       <c r="W8">
-        <v>0.1240103820750296</v>
+        <v>0.1452451577763584</v>
       </c>
       <c r="X8">
-        <v>0.06552945823324163</v>
+        <v>0.09760017563783566</v>
       </c>
       <c r="Y8">
-        <v>0.058480923841788</v>
+        <v>0.04764498213852278</v>
       </c>
       <c r="Z8">
-        <v>0.2097510643037334</v>
+        <v>0.6527873114622739</v>
       </c>
       <c r="AA8">
-        <v>-0.0004628569249262544</v>
+        <v>0.0001018941700629253</v>
       </c>
       <c r="AB8">
-        <v>0.03808923568077165</v>
+        <v>0.0624574804806159</v>
       </c>
       <c r="AC8">
-        <v>-0.0385520926056979</v>
+        <v>-0.06235558631055298</v>
       </c>
       <c r="AD8">
-        <v>554556</v>
+        <v>644060</v>
       </c>
       <c r="AE8">
-        <v>10702.20128360634</v>
+        <v>7744.259601789761</v>
       </c>
       <c r="AF8">
-        <v>565258.2012836064</v>
+        <v>651804.2596017898</v>
       </c>
       <c r="AG8">
-        <v>291004.2012836064</v>
+        <v>34703.25960178976</v>
       </c>
       <c r="AH8">
-        <v>0.6082177777598501</v>
+        <v>0.6236483694936987</v>
       </c>
       <c r="AI8">
-        <v>0.6747561428090184</v>
+        <v>0.69353992517475</v>
       </c>
       <c r="AJ8">
-        <v>0.4442038428319944</v>
+        <v>0.08107365743320735</v>
       </c>
       <c r="AK8">
-        <v>0.5164518612065161</v>
+        <v>0.1075332305179107</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>287.782044628957</v>
+        <v>409.70737913486</v>
       </c>
       <c r="AP8">
-        <v>151.0141158710983</v>
+        <v>22.07586488663471</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.02245</v>
+        <v>0.0367</v>
       </c>
       <c r="E2">
-        <v>0.007904999999999999</v>
+        <v>0.0284</v>
       </c>
       <c r="F2">
-        <v>0.0491</v>
+        <v>0.142</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0009943950271997593</v>
+        <v>0.0008120089321794558</v>
       </c>
       <c r="J2">
-        <v>0.0008058376520526061</v>
+        <v>0.0006581414161158889</v>
       </c>
       <c r="K2">
-        <v>102625.92</v>
+        <v>143409.88</v>
       </c>
       <c r="L2">
-        <v>0.2696192235666501</v>
+        <v>0.3088755765172522</v>
       </c>
       <c r="M2">
-        <v>62862.116</v>
+        <v>60627.054</v>
       </c>
       <c r="N2">
-        <v>0.06475538872682274</v>
+        <v>0.04930038596686218</v>
       </c>
       <c r="O2">
-        <v>0.6125364430350539</v>
+        <v>0.4227536763854763</v>
       </c>
       <c r="P2">
-        <v>29107.116</v>
+        <v>34903.054</v>
       </c>
       <c r="Q2">
-        <v>0.02998376019185739</v>
+        <v>0.02838228018835012</v>
       </c>
       <c r="R2">
-        <v>0.2836234354829657</v>
+        <v>0.2433797029883854</v>
       </c>
       <c r="S2">
-        <v>33755</v>
+        <v>25724</v>
       </c>
       <c r="T2">
-        <v>0.5369688796349139</v>
+        <v>0.4242990266358646</v>
       </c>
       <c r="U2">
-        <v>1360855.5</v>
+        <v>1443627.6</v>
       </c>
       <c r="V2">
-        <v>1.401841562309718</v>
+        <v>1.173921429077107</v>
       </c>
       <c r="W2">
-        <v>0.1023941369513455</v>
+        <v>0.1304019062748213</v>
       </c>
       <c r="X2">
-        <v>0.0958177452565805</v>
+        <v>0.08005634298218035</v>
       </c>
       <c r="Y2">
-        <v>0.006576391694764996</v>
+        <v>0.05034556329264094</v>
       </c>
       <c r="Z2">
-        <v>0.3175608716755457</v>
+        <v>0.2664569993305171</v>
       </c>
       <c r="AA2">
-        <v>0.0009048476687635754</v>
+        <v>0.0001379074559774104</v>
       </c>
       <c r="AB2">
-        <v>0.06233580827874149</v>
+        <v>0.05374826158485733</v>
       </c>
       <c r="AC2">
-        <v>-0.06168891080681541</v>
+        <v>-0.05371672179179192</v>
       </c>
       <c r="AD2">
-        <v>2075375.2</v>
+        <v>2628600.8</v>
       </c>
       <c r="AE2">
-        <v>25501.3281824544</v>
+        <v>30005.74506809724</v>
       </c>
       <c r="AF2">
-        <v>2100876.528182454</v>
+        <v>2658606.545068097</v>
       </c>
       <c r="AG2">
-        <v>740021.0281824544</v>
+        <v>1214978.945068097</v>
       </c>
       <c r="AH2">
-        <v>0.6839594015165582</v>
+        <v>0.6837356195864591</v>
       </c>
       <c r="AI2">
-        <v>0.6812159212677307</v>
+        <v>0.6940264723982867</v>
       </c>
       <c r="AJ2">
-        <v>0.4325625828629178</v>
+        <v>0.4969793938338953</v>
       </c>
       <c r="AK2">
-        <v>0.4294572221564941</v>
+        <v>0.5089830669200758</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>378.8034712202476</v>
+        <v>412.1251231937978</v>
       </c>
       <c r="AP2">
-        <v>135.0707738299515</v>
+        <v>190.4904492968503</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.027</v>
+        <v>0.008</v>
       </c>
       <c r="E3">
-        <v>-0.00953</v>
+        <v>-0.367</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,16 +731,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.01069618415444151</v>
+        <v>0.008052337947771096</v>
       </c>
       <c r="J3">
-        <v>0.008078813465397058</v>
+        <v>0.00597791293629544</v>
       </c>
       <c r="K3">
-        <v>3.92</v>
+        <v>2.68</v>
       </c>
       <c r="L3">
-        <v>0.1232704402515723</v>
+        <v>0.0858974358974359</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>36.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V3">
-        <v>0.8314350797266515</v>
+        <v>0.3274021352313167</v>
       </c>
       <c r="W3">
-        <v>0.05467224546722455</v>
+        <v>0.03912408759124088</v>
       </c>
       <c r="X3">
-        <v>0.08263048010607527</v>
+        <v>0.1248602112289179</v>
       </c>
       <c r="Y3">
-        <v>-0.02795823463885072</v>
+        <v>-0.08573612363767701</v>
       </c>
       <c r="Z3">
-        <v>0.415902072125919</v>
+        <v>0.3465132949535624</v>
       </c>
       <c r="AA3">
-        <v>0.003359995260577412</v>
+        <v>0.002071426308501258</v>
       </c>
       <c r="AB3">
-        <v>0.06034905012138189</v>
+        <v>0.04895256729766347</v>
       </c>
       <c r="AC3">
-        <v>-0.05698905486080447</v>
+        <v>-0.04688114098916221</v>
       </c>
       <c r="AD3">
-        <v>37.2</v>
+        <v>138.5</v>
       </c>
       <c r="AE3">
-        <v>2.124306719443799</v>
+        <v>2.103835280147709</v>
       </c>
       <c r="AF3">
-        <v>39.3243067194438</v>
+        <v>140.6038352801477</v>
       </c>
       <c r="AG3">
-        <v>2.824306719443804</v>
+        <v>131.4038352801477</v>
       </c>
       <c r="AH3">
-        <v>0.4725098744530174</v>
+        <v>0.8334359147595106</v>
       </c>
       <c r="AI3">
-        <v>0.3108043643079736</v>
+        <v>0.6279652829717038</v>
       </c>
       <c r="AJ3">
-        <v>0.0604461985150975</v>
+        <v>0.8238286875632426</v>
       </c>
       <c r="AK3">
-        <v>0.03137271279684067</v>
+        <v>0.6120236981733032</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>48.62745098039216</v>
+        <v>206.1011904761905</v>
       </c>
       <c r="AP3">
-        <v>3.691904208423273</v>
+        <v>195.5414215478389</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bancorp (NYSE:USB)</t>
+          <t>FineMark Holdings, Inc. (OTCPK:FNBT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,13 +844,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0279</v>
+        <v>0.12</v>
       </c>
       <c r="E4">
-        <v>0.0179</v>
-      </c>
-      <c r="F4">
-        <v>0.0491</v>
+        <v>0.184</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,91 +856,88 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.002776566643425367</v>
+        <v>-0.003138563284459354</v>
       </c>
       <c r="J4">
-        <v>0.002193411048770477</v>
+        <v>-0.00243456610329243</v>
       </c>
       <c r="K4">
-        <v>6573</v>
+        <v>22.4</v>
       </c>
       <c r="L4">
-        <v>0.2904294803817604</v>
+        <v>0.2288049029622063</v>
       </c>
       <c r="M4">
-        <v>2818</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04222741365333062</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.4287235661037578</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>2745</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04113351684825853</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.4176175262437243</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>73</v>
-      </c>
-      <c r="T4">
-        <v>0.02590489709013485</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>41652</v>
+        <v>162.1</v>
       </c>
       <c r="V4">
-        <v>0.6241505441761983</v>
+        <v>0.5624566273421235</v>
       </c>
       <c r="W4">
-        <v>0.1375824175824176</v>
+        <v>0.07341855129465748</v>
       </c>
       <c r="X4">
-        <v>0.08422350121924385</v>
+        <v>0.07811393995460128</v>
       </c>
       <c r="Y4">
-        <v>0.05335891636317372</v>
+        <v>-0.004695388659943803</v>
       </c>
       <c r="Z4">
-        <v>0.6663760797694516</v>
+        <v>0.2704148527990738</v>
       </c>
       <c r="AA4">
-        <v>0.001461636656002672</v>
+        <v>-0.0006583428344514371</v>
       </c>
       <c r="AB4">
-        <v>0.06154373930059193</v>
+        <v>0.05108889366185809</v>
       </c>
       <c r="AC4">
-        <v>-0.06008210264458926</v>
+        <v>-0.05174723649630953</v>
       </c>
       <c r="AD4">
-        <v>64109</v>
+        <v>438.1</v>
       </c>
       <c r="AE4">
-        <v>1075.803718629985</v>
+        <v>11.93632672774285</v>
       </c>
       <c r="AF4">
-        <v>65184.80371862998</v>
+        <v>450.0363267277429</v>
       </c>
       <c r="AG4">
-        <v>23532.80371862998</v>
+        <v>287.9363267277429</v>
       </c>
       <c r="AH4">
-        <v>0.4941285949690876</v>
+        <v>0.6096101078126891</v>
       </c>
       <c r="AI4">
-        <v>0.5760267647725187</v>
+        <v>0.6168799417382445</v>
       </c>
       <c r="AJ4">
-        <v>0.2607030361049186</v>
+        <v>0.499771171110009</v>
       </c>
       <c r="AK4">
-        <v>0.3290803975749362</v>
+        <v>0.5074337210453136</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -952,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>230.6079136690647</v>
+        <v>210.625</v>
       </c>
       <c r="AP4">
-        <v>84.65037308859706</v>
+        <v>138.4309263114149</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company (NYSE:WFC)</t>
+          <t>U.S. Bancorp (NYSE:USB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,13 +969,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0251</v>
+        <v>0.0367</v>
       </c>
       <c r="E5">
-        <v>-0.0549</v>
+        <v>-0.0447</v>
       </c>
       <c r="F5">
-        <v>0.104</v>
+        <v>0.01</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,91 +984,91 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.001970894381311234</v>
+        <v>0.003384296672504541</v>
       </c>
       <c r="J5">
-        <v>0.001594970557487413</v>
+        <v>0.002685186291836434</v>
       </c>
       <c r="K5">
-        <v>16068</v>
+        <v>5507</v>
       </c>
       <c r="L5">
-        <v>0.2138977635782748</v>
+        <v>0.2238799902431092</v>
       </c>
       <c r="M5">
-        <v>16898</v>
+        <v>2994</v>
       </c>
       <c r="N5">
-        <v>0.1074012681205477</v>
+        <v>0.04442960489705064</v>
       </c>
       <c r="O5">
-        <v>1.051655464276823</v>
+        <v>0.543671690575631</v>
       </c>
       <c r="P5">
-        <v>3859</v>
+        <v>2935</v>
       </c>
       <c r="Q5">
-        <v>0.02452725137159389</v>
+        <v>0.04355407160081617</v>
       </c>
       <c r="R5">
-        <v>0.2401667911376649</v>
+        <v>0.5329580533865989</v>
       </c>
       <c r="S5">
-        <v>13039</v>
+        <v>59</v>
       </c>
       <c r="T5">
-        <v>0.7716297786720322</v>
+        <v>0.0197060788243153</v>
       </c>
       <c r="U5">
-        <v>220249</v>
+        <v>64354</v>
       </c>
       <c r="V5">
-        <v>1.399871103224199</v>
+        <v>0.9549842329808941</v>
       </c>
       <c r="W5">
-        <v>0.09472213543355361</v>
+        <v>0.1352905048519838</v>
       </c>
       <c r="X5">
-        <v>0.09403531487532535</v>
+        <v>0.07180374105306547</v>
       </c>
       <c r="Y5">
-        <v>0.0006868205582282599</v>
+        <v>0.06348676379891832</v>
       </c>
       <c r="Z5">
-        <v>1.463593347231619</v>
+        <v>0.4014442373272118</v>
       </c>
       <c r="AA5">
-        <v>0.002334388296968885</v>
+        <v>0.001077952563007761</v>
       </c>
       <c r="AB5">
-        <v>0.0634200198115509</v>
+        <v>0.05367101443463453</v>
       </c>
       <c r="AC5">
-        <v>-0.06108563151458202</v>
+        <v>-0.05259306187162677</v>
       </c>
       <c r="AD5">
-        <v>228194</v>
+        <v>72488</v>
       </c>
       <c r="AE5">
-        <v>3999.7320703795</v>
+        <v>1428.765352248666</v>
       </c>
       <c r="AF5">
-        <v>232193.7320703795</v>
+        <v>73916.76535224867</v>
       </c>
       <c r="AG5">
-        <v>11944.73207037951</v>
+        <v>9562.765352248665</v>
       </c>
       <c r="AH5">
-        <v>0.5960885391394422</v>
+        <v>0.5231035678079931</v>
       </c>
       <c r="AI5">
-        <v>0.5654948541126128</v>
+        <v>0.5797631388867447</v>
       </c>
       <c r="AJ5">
-        <v>0.07056200888250233</v>
+        <v>0.1242720256840442</v>
       </c>
       <c r="AK5">
-        <v>0.06275018588006032</v>
+        <v>0.1514515273753821</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1083,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>240.710970464135</v>
+        <v>196.4444444444445</v>
       </c>
       <c r="AP5">
-        <v>12.59992834428219</v>
+        <v>25.91535325812647</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bank of America Corporation (NYSE:BAC)</t>
+          <t>SVB Financial Group (OTCPK:SIVB.Q)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1106,13 +1100,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0179</v>
+        <v>0.252</v>
       </c>
       <c r="E6">
-        <v>0.06</v>
-      </c>
-      <c r="F6">
-        <v>0.0707</v>
+        <v>0.278</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1121,91 +1112,88 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-0.0004744055934391601</v>
+        <v>0.001813922095254842</v>
       </c>
       <c r="J6">
-        <v>-0.0004209447365028792</v>
+        <v>0.00134373878971687</v>
       </c>
       <c r="K6">
-        <v>27409</v>
+        <v>1672</v>
       </c>
       <c r="L6">
-        <v>0.2994995410638577</v>
+        <v>0.288624201622648</v>
       </c>
       <c r="M6">
-        <v>18427.04</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.06935202086540235</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.6722988799299501</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>6819.04</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.02566414379965601</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.2487883541902295</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>11608</v>
-      </c>
-      <c r="T6">
-        <v>0.6299438216881279</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>198376</v>
+        <v>5258</v>
       </c>
       <c r="V6">
-        <v>0.746608054858244</v>
+        <v>2682.65306122449</v>
       </c>
       <c r="W6">
-        <v>0.1100661384691374</v>
+        <v>0.1328038125496426</v>
       </c>
       <c r="X6">
-        <v>0.1073701606033377</v>
+        <v>136.142554534294</v>
       </c>
       <c r="Y6">
-        <v>0.002695977865799656</v>
+        <v>-136.0097507217444</v>
       </c>
       <c r="Z6">
-        <v>0.1854258181968228</v>
+        <v>0.5414292064502675</v>
       </c>
       <c r="AA6">
-        <v>-7.805402218169235e-05</v>
+        <v>0.0007275394265928476</v>
       </c>
       <c r="AB6">
-        <v>0.06221413607686709</v>
+        <v>0.05372384849268101</v>
       </c>
       <c r="AC6">
-        <v>-0.06229219009904879</v>
+        <v>-0.05299630906608816</v>
       </c>
       <c r="AD6">
-        <v>562513</v>
+        <v>19268</v>
       </c>
       <c r="AE6">
-        <v>9802.07851144589</v>
+        <v>372.4597465109435</v>
       </c>
       <c r="AF6">
-        <v>572315.0785114459</v>
+        <v>19640.45974651094</v>
       </c>
       <c r="AG6">
-        <v>373939.0785114459</v>
+        <v>14382.45974651094</v>
       </c>
       <c r="AH6">
-        <v>0.6829388209954101</v>
+        <v>0.9999002159598821</v>
       </c>
       <c r="AI6">
-        <v>0.6798390489586479</v>
+        <v>0.5465481695532748</v>
       </c>
       <c r="AJ6">
-        <v>0.5846067528603882</v>
+        <v>0.9998637414623225</v>
       </c>
       <c r="AK6">
-        <v>0.5811352523543343</v>
+        <v>0.4688282493190041</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1214,10 +1202,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>293.434011476265</v>
+        <v>226.6823529411765</v>
       </c>
       <c r="AP6">
-        <v>195.0647253580834</v>
+        <v>169.2054087824817</v>
       </c>
     </row>
     <row r="7">
@@ -1237,13 +1225,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0179</v>
-      </c>
-      <c r="E7">
-        <v>-0.00209</v>
+        <v>0.019</v>
       </c>
       <c r="F7">
-        <v>-0.116</v>
+        <v>0.0791</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1252,91 +1237,91 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.002650732251117159</v>
+        <v>0.001885516277239551</v>
       </c>
       <c r="J7">
-        <v>0.00213997116723661</v>
+        <v>0.001422767106774031</v>
       </c>
       <c r="K7">
-        <v>15505</v>
+        <v>13580</v>
       </c>
       <c r="L7">
-        <v>0.2191581387459716</v>
+        <v>0.1871864145117715</v>
       </c>
       <c r="M7">
-        <v>7702.276</v>
+        <v>5700.634</v>
       </c>
       <c r="N7">
-        <v>0.0879216107958664</v>
+        <v>0.05790379085445316</v>
       </c>
       <c r="O7">
-        <v>0.4967607868429539</v>
+        <v>0.4197815905743741</v>
       </c>
       <c r="P7">
-        <v>3951.276</v>
+        <v>3942.634</v>
       </c>
       <c r="Q7">
-        <v>0.04510388236140173</v>
+        <v>0.0400470289009356</v>
       </c>
       <c r="R7">
-        <v>0.2548388261851016</v>
+        <v>0.2903265095729013</v>
       </c>
       <c r="S7">
-        <v>3751</v>
+        <v>1758</v>
       </c>
       <c r="T7">
-        <v>0.4869989078552884</v>
+        <v>0.3083867513683565</v>
       </c>
       <c r="U7">
-        <v>283441</v>
+        <v>235051</v>
       </c>
       <c r="V7">
-        <v>3.235483808369263</v>
+        <v>2.387514080737348</v>
       </c>
       <c r="W7">
-        <v>0.0847823709536308</v>
+        <v>0.07562721020243365</v>
       </c>
       <c r="X7">
-        <v>0.195050704520092</v>
+        <v>0.1442659015959848</v>
       </c>
       <c r="Y7">
-        <v>-0.1102683335664612</v>
+        <v>-0.06863869139355119</v>
       </c>
       <c r="Z7">
-        <v>0.1626464350797467</v>
+        <v>0.1527033614546918</v>
       </c>
       <c r="AA7">
-        <v>0.000348058681524479</v>
+        <v>0.000217261319771561</v>
       </c>
       <c r="AB7">
-        <v>0.06268975595117486</v>
+        <v>0.05328535116359653</v>
       </c>
       <c r="AC7">
-        <v>-0.06234169726965038</v>
+        <v>-0.05306808984382497</v>
       </c>
       <c r="AD7">
-        <v>576462</v>
+        <v>630457</v>
       </c>
       <c r="AE7">
-        <v>2877.329973489816</v>
+        <v>2836.047825594125</v>
       </c>
       <c r="AF7">
-        <v>579339.3299734899</v>
+        <v>633293.0478255941</v>
       </c>
       <c r="AG7">
-        <v>295898.3299734899</v>
+        <v>398242.0478255941</v>
       </c>
       <c r="AH7">
-        <v>0.8686486404495295</v>
+        <v>0.8654581183403649</v>
       </c>
       <c r="AI7">
-        <v>0.7442155811016645</v>
+        <v>0.7508026337280579</v>
       </c>
       <c r="AJ7">
-        <v>0.7715687337566309</v>
+        <v>0.8017884912596419</v>
       </c>
       <c r="AK7">
-        <v>0.5977558917000337</v>
+        <v>0.65453287114717</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1345,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>755.5203145478375</v>
+        <v>895.5355113636364</v>
       </c>
       <c r="AP7">
-        <v>387.8090825340627</v>
+        <v>565.6847270249916</v>
       </c>
     </row>
     <row r="8">
@@ -1359,127 +1344,1154 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Bank of America Corporation (NYSE:BAC)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0236</v>
+      </c>
+      <c r="E8">
+        <v>0.05599999999999999</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.0003773423571590488</v>
+      </c>
+      <c r="J8">
+        <v>0.0003475788591400413</v>
+      </c>
+      <c r="K8">
+        <v>30503</v>
+      </c>
+      <c r="L8">
+        <v>0.3152048113090564</v>
+      </c>
+      <c r="M8">
+        <v>11885.33</v>
+      </c>
+      <c r="N8">
+        <v>0.04460532606957862</v>
+      </c>
+      <c r="O8">
+        <v>0.3896446251188408</v>
+      </c>
+      <c r="P8">
+        <v>7122.33</v>
+      </c>
+      <c r="Q8">
+        <v>0.02672991427458404</v>
+      </c>
+      <c r="R8">
+        <v>0.2334960495688949</v>
+      </c>
+      <c r="S8">
+        <v>4763</v>
+      </c>
+      <c r="T8">
+        <v>0.4007461298929016</v>
+      </c>
+      <c r="U8">
+        <v>345626</v>
+      </c>
+      <c r="V8">
+        <v>1.297125147398026</v>
+      </c>
+      <c r="W8">
+        <v>0.1268896376721161</v>
+      </c>
+      <c r="X8">
+        <v>0.09208629732141724</v>
+      </c>
+      <c r="Y8">
+        <v>0.0348033403506989</v>
+      </c>
+      <c r="Z8">
+        <v>0.1684613164567303</v>
+      </c>
+      <c r="AA8">
+        <v>5.855359218325977e-05</v>
+      </c>
+      <c r="AB8">
+        <v>0.05316607740271752</v>
+      </c>
+      <c r="AC8">
+        <v>-0.05310752381053426</v>
+      </c>
+      <c r="AD8">
+        <v>680417</v>
+      </c>
+      <c r="AE8">
+        <v>9807.419127065023</v>
+      </c>
+      <c r="AF8">
+        <v>690224.419127065</v>
+      </c>
+      <c r="AG8">
+        <v>344598.419127065</v>
+      </c>
+      <c r="AH8">
+        <v>0.7214790208043369</v>
+      </c>
+      <c r="AI8">
+        <v>0.706264809464936</v>
+      </c>
+      <c r="AJ8">
+        <v>0.5639411919875552</v>
+      </c>
+      <c r="AK8">
+        <v>0.5455420628051416</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>340.5490490490491</v>
+      </c>
+      <c r="AP8">
+        <v>172.4716812447773</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>JPMorgan Chase &amp; Co. (NYSE:JPM)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.0508</v>
-      </c>
-      <c r="E8">
-        <v>0.0659</v>
-      </c>
-      <c r="F8">
-        <v>-0.008489999999999999</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.0001919648351125582</v>
-      </c>
-      <c r="J8">
-        <v>0.0001560909170165664</v>
-      </c>
-      <c r="K8">
-        <v>37067</v>
-      </c>
-      <c r="L8">
-        <v>0.3073931251814073</v>
-      </c>
-      <c r="M8">
-        <v>17016.8</v>
-      </c>
-      <c r="N8">
-        <v>0.043262009626209</v>
-      </c>
-      <c r="O8">
-        <v>0.4590822024981789</v>
-      </c>
-      <c r="P8">
-        <v>11732.8</v>
-      </c>
-      <c r="Q8">
-        <v>0.02982843463767482</v>
-      </c>
-      <c r="R8">
-        <v>0.3165295276121617</v>
-      </c>
-      <c r="S8">
-        <v>5284</v>
-      </c>
-      <c r="T8">
-        <v>0.3105166658831273</v>
-      </c>
-      <c r="U8">
-        <v>617101</v>
-      </c>
-      <c r="V8">
-        <v>1.568863088379907</v>
-      </c>
-      <c r="W8">
-        <v>0.1452451577763584</v>
-      </c>
-      <c r="X8">
-        <v>0.09760017563783566</v>
-      </c>
-      <c r="Y8">
-        <v>0.04764498213852278</v>
-      </c>
-      <c r="Z8">
-        <v>0.6527873114622739</v>
-      </c>
-      <c r="AA8">
-        <v>0.0001018941700629253</v>
-      </c>
-      <c r="AB8">
-        <v>0.0624574804806159</v>
-      </c>
-      <c r="AC8">
-        <v>-0.06235558631055298</v>
-      </c>
-      <c r="AD8">
-        <v>644060</v>
-      </c>
-      <c r="AE8">
-        <v>7744.259601789761</v>
-      </c>
-      <c r="AF8">
-        <v>651804.2596017898</v>
-      </c>
-      <c r="AG8">
-        <v>34703.25960178976</v>
-      </c>
-      <c r="AH8">
-        <v>0.6236483694936987</v>
-      </c>
-      <c r="AI8">
-        <v>0.69353992517475</v>
-      </c>
-      <c r="AJ8">
-        <v>0.08107365743320735</v>
-      </c>
-      <c r="AK8">
-        <v>0.1075332305179107</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>409.70737913486</v>
-      </c>
-      <c r="AP8">
-        <v>22.07586488663471</v>
+      <c r="D9">
+        <v>0.06759999999999999</v>
+      </c>
+      <c r="E9">
+        <v>0.116</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.0001376591069739018</v>
+      </c>
+      <c r="J9">
+        <v>0.0001110690963860868</v>
+      </c>
+      <c r="K9">
+        <v>51253</v>
+      </c>
+      <c r="L9">
+        <v>0.3598444158926076</v>
+      </c>
+      <c r="M9">
+        <v>19257.55</v>
+      </c>
+      <c r="N9">
+        <v>0.03916042463760306</v>
+      </c>
+      <c r="O9">
+        <v>0.3757350789222094</v>
+      </c>
+      <c r="P9">
+        <v>11708.55</v>
+      </c>
+      <c r="Q9">
+        <v>0.02380945602584998</v>
+      </c>
+      <c r="R9">
+        <v>0.2284461397381617</v>
+      </c>
+      <c r="S9">
+        <v>7549</v>
+      </c>
+      <c r="T9">
+        <v>0.3920020978784944</v>
+      </c>
+      <c r="U9">
+        <v>488231</v>
+      </c>
+      <c r="V9">
+        <v>0.9928227256967569</v>
+      </c>
+      <c r="W9">
+        <v>0.2008503801238342</v>
+      </c>
+      <c r="X9">
+        <v>0.07766460929666422</v>
+      </c>
+      <c r="Y9">
+        <v>0.1231857708271699</v>
+      </c>
+      <c r="Z9">
+        <v>0.5250371138738917</v>
+      </c>
+      <c r="AA9">
+        <v>5.83153978071321e-05</v>
+      </c>
+      <c r="AB9">
+        <v>0.05377267467703364</v>
+      </c>
+      <c r="AC9">
+        <v>-0.05371435927922651</v>
+      </c>
+      <c r="AD9">
+        <v>743872</v>
+      </c>
+      <c r="AE9">
+        <v>7761.965378673001</v>
+      </c>
+      <c r="AF9">
+        <v>751633.965378673</v>
+      </c>
+      <c r="AG9">
+        <v>263402.965378673</v>
+      </c>
+      <c r="AH9">
+        <v>0.6045016173928075</v>
+      </c>
+      <c r="AI9">
+        <v>0.7031155043441937</v>
+      </c>
+      <c r="AJ9">
+        <v>0.3488025804407671</v>
+      </c>
+      <c r="AK9">
+        <v>0.4535378324111524</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>473.2010178117048</v>
+      </c>
+      <c r="AP9">
+        <v>167.5591382815986</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>The PNC Financial Services Group, Inc. (NYSE:PNC)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.047</v>
+      </c>
+      <c r="E10">
+        <v>0.00647</v>
+      </c>
+      <c r="F10">
+        <v>0.15</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0.001947513039822188</v>
+      </c>
+      <c r="J10">
+        <v>0.001625588773784402</v>
+      </c>
+      <c r="K10">
+        <v>6242</v>
+      </c>
+      <c r="L10">
+        <v>0.2976065605034805</v>
+      </c>
+      <c r="M10">
+        <v>3701</v>
+      </c>
+      <c r="N10">
+        <v>0.06000022696654351</v>
+      </c>
+      <c r="O10">
+        <v>0.5929189362383851</v>
+      </c>
+      <c r="P10">
+        <v>2449</v>
+      </c>
+      <c r="Q10">
+        <v>0.03970293321833696</v>
+      </c>
+      <c r="R10">
+        <v>0.3923421980134572</v>
+      </c>
+      <c r="S10">
+        <v>1252</v>
+      </c>
+      <c r="T10">
+        <v>0.3382869494731154</v>
+      </c>
+      <c r="U10">
+        <v>4782</v>
+      </c>
+      <c r="V10">
+        <v>0.07752528650473145</v>
+      </c>
+      <c r="W10">
+        <v>0.1582496704188216</v>
+      </c>
+      <c r="X10">
+        <v>0.07305166612719399</v>
+      </c>
+      <c r="Y10">
+        <v>0.08519800429162763</v>
+      </c>
+      <c r="Z10">
+        <v>0.2287571184173761</v>
+      </c>
+      <c r="AA10">
+        <v>0.0003718650036225557</v>
+      </c>
+      <c r="AB10">
+        <v>0.05409094930797988</v>
+      </c>
+      <c r="AC10">
+        <v>-0.05371908430435733</v>
+      </c>
+      <c r="AD10">
+        <v>71392</v>
+      </c>
+      <c r="AE10">
+        <v>1935.764307513847</v>
+      </c>
+      <c r="AF10">
+        <v>73327.76430751385</v>
+      </c>
+      <c r="AG10">
+        <v>68545.76430751385</v>
+      </c>
+      <c r="AH10">
+        <v>0.5431249157882244</v>
+      </c>
+      <c r="AI10">
+        <v>0.5970890165778454</v>
+      </c>
+      <c r="AJ10">
+        <v>0.5263484763689131</v>
+      </c>
+      <c r="AK10">
+        <v>0.5807645808955729</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>166.803738317757</v>
+      </c>
+      <c r="AP10">
+        <v>160.1536549240978</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wells Fargo &amp; Company (NYSE:WFC)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>-0.0226</v>
+      </c>
+      <c r="E11">
+        <v>-0.0397</v>
+      </c>
+      <c r="F11">
+        <v>0.142</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0.001001588391751439</v>
+      </c>
+      <c r="J11">
+        <v>0.00087850127160366</v>
+      </c>
+      <c r="K11">
+        <v>18356</v>
+      </c>
+      <c r="L11">
+        <v>0.2399728076138681</v>
+      </c>
+      <c r="M11">
+        <v>14169</v>
+      </c>
+      <c r="N11">
+        <v>0.0792674432850926</v>
+      </c>
+      <c r="O11">
+        <v>0.7719001961211593</v>
+      </c>
+      <c r="P11">
+        <v>4662</v>
+      </c>
+      <c r="Q11">
+        <v>0.02608122101736902</v>
+      </c>
+      <c r="R11">
+        <v>0.2539769012856832</v>
+      </c>
+      <c r="S11">
+        <v>9507</v>
+      </c>
+      <c r="T11">
+        <v>0.6709718399322464</v>
+      </c>
+      <c r="U11">
+        <v>287530</v>
+      </c>
+      <c r="V11">
+        <v>1.608565739837862</v>
+      </c>
+      <c r="W11">
+        <v>0.1170827539578257</v>
+      </c>
+      <c r="X11">
+        <v>0.08052504946562736</v>
+      </c>
+      <c r="Y11">
+        <v>0.03655770449219836</v>
+      </c>
+      <c r="Z11">
+        <v>0.4692935425572848</v>
+      </c>
+      <c r="AA11">
+        <v>0.000412274973891961</v>
+      </c>
+      <c r="AB11">
+        <v>0.05425019837084542</v>
+      </c>
+      <c r="AC11">
+        <v>-0.05383792339695346</v>
+      </c>
+      <c r="AD11">
+        <v>306828</v>
+      </c>
+      <c r="AE11">
+        <v>4031.932503690744</v>
+      </c>
+      <c r="AF11">
+        <v>310859.9325036908</v>
+      </c>
+      <c r="AG11">
+        <v>23329.93250369077</v>
+      </c>
+      <c r="AH11">
+        <v>0.6349143599969747</v>
+      </c>
+      <c r="AI11">
+        <v>0.6302497502057299</v>
+      </c>
+      <c r="AJ11">
+        <v>0.1154494314662674</v>
+      </c>
+      <c r="AK11">
+        <v>0.1134156534364048</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>347.4835787089468</v>
+      </c>
+      <c r="AP11">
+        <v>26.42121461346633</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>First Citizens BancShares, Inc. (NasdaqGS:FCNC.A)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.333</v>
+      </c>
+      <c r="E12">
+        <v>0.983</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>-0.002153025418092073</v>
+      </c>
+      <c r="J12">
+        <v>-0.002052846368781392</v>
+      </c>
+      <c r="K12">
+        <v>11209</v>
+      </c>
+      <c r="L12">
+        <v>1.734870763039777</v>
+      </c>
+      <c r="M12">
+        <v>493</v>
+      </c>
+      <c r="N12">
+        <v>0.02408531968010005</v>
+      </c>
+      <c r="O12">
+        <v>0.04398251405120885</v>
+      </c>
+      <c r="P12">
+        <v>45</v>
+      </c>
+      <c r="Q12">
+        <v>0.002198457171611567</v>
+      </c>
+      <c r="R12">
+        <v>0.004014631100008922</v>
+      </c>
+      <c r="S12">
+        <v>448</v>
+      </c>
+      <c r="T12">
+        <v>0.9087221095334685</v>
+      </c>
+      <c r="U12">
+        <v>791</v>
+      </c>
+      <c r="V12">
+        <v>0.03864399161654998</v>
+      </c>
+      <c r="W12">
+        <v>1.252122430741734</v>
+      </c>
+      <c r="X12">
+        <v>0.08358924604340176</v>
+      </c>
+      <c r="Y12">
+        <v>1.168533184698332</v>
+      </c>
+      <c r="Z12">
+        <v>0.3346705394715251</v>
+      </c>
+      <c r="AA12">
+        <v>-0.00068702720169223</v>
+      </c>
+      <c r="AB12">
+        <v>0.05347088440834787</v>
+      </c>
+      <c r="AC12">
+        <v>-0.0541579116100401</v>
+      </c>
+      <c r="AD12">
+        <v>39906</v>
+      </c>
+      <c r="AE12">
+        <v>309.5534861314644</v>
+      </c>
+      <c r="AF12">
+        <v>40215.55348613147</v>
+      </c>
+      <c r="AG12">
+        <v>39424.55348613147</v>
+      </c>
+      <c r="AH12">
+        <v>0.6626994423756677</v>
+      </c>
+      <c r="AI12">
+        <v>0.6635731339120294</v>
+      </c>
+      <c r="AJ12">
+        <v>0.6582447862229276</v>
+      </c>
+      <c r="AK12">
+        <v>0.6591240812213665</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>831.375</v>
+      </c>
+      <c r="AP12">
+        <v>821.3448642944055</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KeyCorp (NYSE:KEY)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>-0.0015</v>
+      </c>
+      <c r="E13">
+        <v>-0.0386</v>
+      </c>
+      <c r="F13">
+        <v>0.2</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0.004081099229443008</v>
+      </c>
+      <c r="J13">
+        <v>0.003354647999790089</v>
+      </c>
+      <c r="K13">
+        <v>1296</v>
+      </c>
+      <c r="L13">
+        <v>0.2127729436874077</v>
+      </c>
+      <c r="M13">
+        <v>837</v>
+      </c>
+      <c r="N13">
+        <v>0.06208231655305924</v>
+      </c>
+      <c r="O13">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="P13">
+        <v>765</v>
+      </c>
+      <c r="Q13">
+        <v>0.05674190222591436</v>
+      </c>
+      <c r="R13">
+        <v>0.5902777777777778</v>
+      </c>
+      <c r="S13">
+        <v>72</v>
+      </c>
+      <c r="T13">
+        <v>0.08602150537634409</v>
+      </c>
+      <c r="U13">
+        <v>766</v>
+      </c>
+      <c r="V13">
+        <v>0.0568160746471247</v>
+      </c>
+      <c r="W13">
+        <v>0.1201112140871177</v>
+      </c>
+      <c r="X13">
+        <v>0.08418076022807956</v>
+      </c>
+      <c r="Y13">
+        <v>0.03593045385903813</v>
+      </c>
+      <c r="Z13">
+        <v>0.1560845952577727</v>
+      </c>
+      <c r="AA13">
+        <v>0.0005236088752795327</v>
+      </c>
+      <c r="AB13">
+        <v>0.05478189409637468</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05425828522109515</v>
+      </c>
+      <c r="AD13">
+        <v>26530</v>
+      </c>
+      <c r="AE13">
+        <v>545.7101229673132</v>
+      </c>
+      <c r="AF13">
+        <v>27075.71012296731</v>
+      </c>
+      <c r="AG13">
+        <v>26309.71012296731</v>
+      </c>
+      <c r="AH13">
+        <v>0.667583137276801</v>
+      </c>
+      <c r="AI13">
+        <v>0.6696652216940708</v>
+      </c>
+      <c r="AJ13">
+        <v>0.6611840487191533</v>
+      </c>
+      <c r="AK13">
+        <v>0.6632859979414163</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>197.9850746268657</v>
+      </c>
+      <c r="AP13">
+        <v>196.3411203206516</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fifth Third Bancorp (NasdaqGS:FITB)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.0387</v>
+      </c>
+      <c r="E14">
+        <v>0.0275</v>
+      </c>
+      <c r="F14">
+        <v>0.173</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>-0.002940934720795005</v>
+      </c>
+      <c r="J14">
+        <v>-0.002311509577599027</v>
+      </c>
+      <c r="K14">
+        <v>2556</v>
+      </c>
+      <c r="L14">
+        <v>0.3105333495322561</v>
+      </c>
+      <c r="M14">
+        <v>1212.54</v>
+      </c>
+      <c r="N14">
+        <v>0.05162314854629752</v>
+      </c>
+      <c r="O14">
+        <v>0.4743896713615023</v>
+      </c>
+      <c r="P14">
+        <v>912.5400000000001</v>
+      </c>
+      <c r="Q14">
+        <v>0.03885083211641541</v>
+      </c>
+      <c r="R14">
+        <v>0.357018779342723</v>
+      </c>
+      <c r="S14">
+        <v>299.9999999999999</v>
+      </c>
+      <c r="T14">
+        <v>0.2474145182839328</v>
+      </c>
+      <c r="U14">
+        <v>2837</v>
+      </c>
+      <c r="V14">
+        <v>0.1207835390385852</v>
+      </c>
+      <c r="W14">
+        <v>0.1748290013679891</v>
+      </c>
+      <c r="X14">
+        <v>0.07162330248824472</v>
+      </c>
+      <c r="Y14">
+        <v>0.1032056988797443</v>
+      </c>
+      <c r="Z14">
+        <v>0.2511899236216307</v>
+      </c>
+      <c r="AA14">
+        <v>-0.0005806279142477672</v>
+      </c>
+      <c r="AB14">
+        <v>0.05473086401552545</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05531149192977321</v>
+      </c>
+      <c r="AD14">
+        <v>24881</v>
+      </c>
+      <c r="AE14">
+        <v>571.0341684343184</v>
+      </c>
+      <c r="AF14">
+        <v>25452.03416843432</v>
+      </c>
+      <c r="AG14">
+        <v>22615.03416843432</v>
+      </c>
+      <c r="AH14">
+        <v>0.5200625333051045</v>
+      </c>
+      <c r="AI14">
+        <v>0.6060580402985993</v>
+      </c>
+      <c r="AJ14">
+        <v>0.4905292551252878</v>
+      </c>
+      <c r="AK14">
+        <v>0.5775176698986121</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>276.4555555555556</v>
+      </c>
+      <c r="AP14">
+        <v>251.278157427048</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Comerica Incorporated (NYSE:CMA)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.0243</v>
+      </c>
+      <c r="E15">
+        <v>0.0293</v>
+      </c>
+      <c r="F15">
+        <v>-0.09849999999999999</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>-0.003510019754581721</v>
+      </c>
+      <c r="J15">
+        <v>-0.002734072604674188</v>
+      </c>
+      <c r="K15">
+        <v>1198</v>
+      </c>
+      <c r="L15">
+        <v>0.3220430107526882</v>
+      </c>
+      <c r="M15">
+        <v>377</v>
+      </c>
+      <c r="N15">
+        <v>0.05122421804940352</v>
+      </c>
+      <c r="O15">
+        <v>0.3146911519198665</v>
+      </c>
+      <c r="P15">
+        <v>361</v>
+      </c>
+      <c r="Q15">
+        <v>0.04905024593059594</v>
+      </c>
+      <c r="R15">
+        <v>0.3013355592654424</v>
+      </c>
+      <c r="S15">
+        <v>16</v>
+      </c>
+      <c r="T15">
+        <v>0.04244031830238727</v>
+      </c>
+      <c r="U15">
+        <v>8112</v>
+      </c>
+      <c r="V15">
+        <v>1.102203864235441</v>
+      </c>
+      <c r="W15">
+        <v>0.2562566844919786</v>
+      </c>
+      <c r="X15">
+        <v>0.07958763649873335</v>
+      </c>
+      <c r="Y15">
+        <v>0.1766690479932453</v>
+      </c>
+      <c r="Z15">
+        <v>1.082249077424332</v>
+      </c>
+      <c r="AA15">
+        <v>-0.00295894755401978</v>
+      </c>
+      <c r="AB15">
+        <v>0.05491595607353575</v>
+      </c>
+      <c r="AC15">
+        <v>-0.05787490362755553</v>
+      </c>
+      <c r="AD15">
+        <v>11911</v>
+      </c>
+      <c r="AE15">
+        <v>380.28636743522</v>
+      </c>
+      <c r="AF15">
+        <v>12291.28636743522</v>
+      </c>
+      <c r="AG15">
+        <v>4179.286367435219</v>
+      </c>
+      <c r="AH15">
+        <v>0.6254761766150351</v>
+      </c>
+      <c r="AI15">
+        <v>0.7119899482534806</v>
+      </c>
+      <c r="AJ15">
+        <v>0.3621852055141646</v>
+      </c>
+      <c r="AK15">
+        <v>0.456688404190604</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>189.0634920634921</v>
+      </c>
+      <c r="AP15">
+        <v>66.33787884817808</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Oakworth Capital Inc. (OTCPK:OAKC)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>-0.01315582238825996</v>
+      </c>
+      <c r="J16">
+        <v>-0.009999991184409505</v>
+      </c>
+      <c r="K16">
+        <v>12.8</v>
+      </c>
+      <c r="L16">
+        <v>0.2265486725663717</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>-0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>-0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>118.3</v>
+      </c>
+      <c r="V16">
+        <v>0.816988950276243</v>
+      </c>
+      <c r="W16">
+        <v>0.128</v>
+      </c>
+      <c r="X16">
+        <v>0.06487623101817613</v>
+      </c>
+      <c r="Y16">
+        <v>0.06312376898182387</v>
+      </c>
+      <c r="Z16">
+        <v>2.151027253595478</v>
+      </c>
+      <c r="AA16">
+        <v>-0.02151025357337937</v>
+      </c>
+      <c r="AB16">
+        <v>0.055730004817606</v>
+      </c>
+      <c r="AC16">
+        <v>-0.07724025839098536</v>
+      </c>
+      <c r="AD16">
+        <v>74.2</v>
+      </c>
+      <c r="AE16">
+        <v>10.76651982468344</v>
+      </c>
+      <c r="AF16">
+        <v>84.96651982468344</v>
+      </c>
+      <c r="AG16">
+        <v>-33.33348017531655</v>
+      </c>
+      <c r="AH16">
+        <v>0.3697950418952014</v>
+      </c>
+      <c r="AI16">
+        <v>0.4320334742305201</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.2990447735135541</v>
+      </c>
+      <c r="AK16">
+        <v>-0.4253535853051542</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>52.62411347517731</v>
+      </c>
+      <c r="AP16">
+        <v>-23.64076608178479</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0367</v>
+        <v>0.0186</v>
       </c>
       <c r="E2">
-        <v>0.0284</v>
+        <v>-0.0447</v>
       </c>
       <c r="F2">
-        <v>0.142</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0008120089321794558</v>
+        <v>-0.0008316340642067157</v>
       </c>
       <c r="J2">
-        <v>0.0006581414161158889</v>
+        <v>-0.0006821152868553484</v>
       </c>
       <c r="K2">
-        <v>143409.88</v>
+        <v>117019</v>
       </c>
       <c r="L2">
-        <v>0.3088755765172522</v>
+        <v>0.2514299097147916</v>
       </c>
       <c r="M2">
-        <v>60627.054</v>
+        <v>85726.227</v>
       </c>
       <c r="N2">
-        <v>0.04930038596686218</v>
+        <v>0.05413071048721489</v>
       </c>
       <c r="O2">
-        <v>0.4227536763854763</v>
+        <v>0.7325838282672045</v>
       </c>
       <c r="P2">
-        <v>34903.054</v>
+        <v>37285.227</v>
       </c>
       <c r="Q2">
-        <v>0.02838228018835012</v>
+        <v>0.02354327139799454</v>
       </c>
       <c r="R2">
-        <v>0.2433797029883854</v>
+        <v>0.3186254112580008</v>
       </c>
       <c r="S2">
-        <v>25724</v>
+        <v>48441</v>
       </c>
       <c r="T2">
-        <v>0.4242990266358646</v>
+        <v>0.5650662777915095</v>
       </c>
       <c r="U2">
-        <v>1443627.6</v>
+        <v>1359460</v>
       </c>
       <c r="V2">
-        <v>1.173921429077107</v>
+        <v>0.858413326401839</v>
       </c>
       <c r="W2">
-        <v>0.1304019062748213</v>
+        <v>0.1184105388187021</v>
       </c>
       <c r="X2">
-        <v>0.08005634298218035</v>
+        <v>0.07771961002369931</v>
       </c>
       <c r="Y2">
-        <v>0.05034556329264094</v>
+        <v>0.04069092879500277</v>
       </c>
       <c r="Z2">
-        <v>0.2664569993305171</v>
+        <v>0.2217526126743046</v>
       </c>
       <c r="AA2">
-        <v>0.0001379074559774104</v>
+        <v>0.0002197161760174885</v>
       </c>
       <c r="AB2">
-        <v>0.05374826158485733</v>
+        <v>0.05843630650270522</v>
       </c>
       <c r="AC2">
-        <v>-0.05371672179179192</v>
+        <v>-0.05823625220848661</v>
       </c>
       <c r="AD2">
-        <v>2628600.8</v>
+        <v>2882989</v>
       </c>
       <c r="AE2">
-        <v>30005.74506809724</v>
+        <v>33500.27068179353</v>
       </c>
       <c r="AF2">
-        <v>2658606.545068097</v>
+        <v>2916489.270681793</v>
       </c>
       <c r="AG2">
-        <v>1214978.945068097</v>
+        <v>1557029.270681793</v>
       </c>
       <c r="AH2">
-        <v>0.6837356195864591</v>
+        <v>0.6480830093459902</v>
       </c>
       <c r="AI2">
-        <v>0.6940264723982867</v>
+        <v>0.7089522244340719</v>
       </c>
       <c r="AJ2">
-        <v>0.4969793938338953</v>
+        <v>0.4957557436748592</v>
       </c>
       <c r="AK2">
-        <v>0.5089830669200758</v>
+        <v>0.5652998493525555</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>412.1251231937978</v>
+        <v>456.6749564390939</v>
       </c>
       <c r="AP2">
-        <v>190.4904492968503</v>
+        <v>246.6385665581805</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CIB Marine Bancshares, Inc. (OTCPK:CIBH)</t>
+          <t>Citigroup Inc. (NYSE:C)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.008</v>
+        <v>0.0127</v>
       </c>
       <c r="E3">
-        <v>-0.367</v>
+        <v>-0.157</v>
+      </c>
+      <c r="F3">
+        <v>0.258</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,88 +734,91 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.008052337947771096</v>
+        <v>0.002551180986686265</v>
       </c>
       <c r="J3">
-        <v>0.00597791293629544</v>
+        <v>0.001863523101126724</v>
       </c>
       <c r="K3">
-        <v>2.68</v>
+        <v>7987</v>
       </c>
       <c r="L3">
-        <v>0.0858974358974359</v>
+        <v>0.1152392220234316</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>6573.295</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04937645585651498</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.8229992487792663</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>4066.295</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03054468657911559</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.5091141855515212</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2507</v>
+      </c>
+      <c r="T3">
+        <v>0.3813916764727584</v>
       </c>
       <c r="U3">
-        <v>9.199999999999999</v>
+        <v>283023</v>
       </c>
       <c r="V3">
-        <v>0.3274021352313167</v>
+        <v>2.12597679944053</v>
       </c>
       <c r="W3">
-        <v>0.03912408759124088</v>
+        <v>0.042035072207486</v>
       </c>
       <c r="X3">
-        <v>0.1248602112289179</v>
+        <v>0.1271511942237079</v>
       </c>
       <c r="Y3">
-        <v>-0.08573612363767701</v>
+        <v>-0.08511612201622185</v>
       </c>
       <c r="Z3">
-        <v>0.3465132949535624</v>
+        <v>0.117903650287267</v>
       </c>
       <c r="AA3">
-        <v>0.002071426308501258</v>
+        <v>0.0002197161760174885</v>
       </c>
       <c r="AB3">
-        <v>0.04895256729766347</v>
+        <v>0.05637995120573513</v>
       </c>
       <c r="AC3">
-        <v>-0.04688114098916221</v>
+        <v>-0.05616023502971765</v>
       </c>
       <c r="AD3">
-        <v>138.5</v>
+        <v>666387</v>
       </c>
       <c r="AE3">
-        <v>2.103835280147709</v>
+        <v>2755.913740873742</v>
       </c>
       <c r="AF3">
-        <v>140.6038352801477</v>
+        <v>669142.9137408737</v>
       </c>
       <c r="AG3">
-        <v>131.4038352801477</v>
+        <v>386119.9137408737</v>
       </c>
       <c r="AH3">
-        <v>0.8334359147595106</v>
+        <v>0.8340630166192625</v>
       </c>
       <c r="AI3">
-        <v>0.6279652829717038</v>
+        <v>0.7612158415128771</v>
       </c>
       <c r="AJ3">
-        <v>0.8238286875632426</v>
+        <v>0.7436165199595819</v>
       </c>
       <c r="AK3">
-        <v>0.6120236981733032</v>
+        <v>0.6478283848951619</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>206.1011904761905</v>
+        <v>915.3667582417582</v>
       </c>
       <c r="AP3">
-        <v>195.5414215478389</v>
+        <v>530.3844968968045</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FineMark Holdings, Inc. (OTCPK:FNBT)</t>
+          <t>U.S. Bancorp (NYSE:USB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +850,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.12</v>
+        <v>0.0316</v>
       </c>
       <c r="E4">
-        <v>0.184</v>
+        <v>-0.0552</v>
+      </c>
+      <c r="F4">
+        <v>0.0585</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,88 +865,91 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.003138563284459354</v>
+        <v>0.004351021264802606</v>
       </c>
       <c r="J4">
-        <v>-0.00243456610329243</v>
+        <v>0.003531486161110188</v>
       </c>
       <c r="K4">
-        <v>22.4</v>
+        <v>5483</v>
       </c>
       <c r="L4">
-        <v>0.2288049029622063</v>
+        <v>0.2202273366269028</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>3126</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.04189433139943953</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.5701258435163232</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>3058</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.04098300237347603</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.5577238737917198</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="T4">
+        <v>0.0217530390275112</v>
       </c>
       <c r="U4">
-        <v>162.1</v>
+        <v>73562</v>
       </c>
       <c r="V4">
-        <v>0.5624566273421235</v>
+        <v>0.9858703795283336</v>
       </c>
       <c r="W4">
-        <v>0.07341855129465748</v>
+        <v>0.1184105388187021</v>
       </c>
       <c r="X4">
-        <v>0.07811393995460128</v>
+        <v>0.07719536702552725</v>
       </c>
       <c r="Y4">
-        <v>-0.004695388659943803</v>
+        <v>0.04121517179317484</v>
       </c>
       <c r="Z4">
-        <v>0.2704148527990738</v>
+        <v>0.4967640292133212</v>
       </c>
       <c r="AA4">
-        <v>-0.0006583428344514371</v>
+        <v>0.001754315294504181</v>
       </c>
       <c r="AB4">
-        <v>0.05108889366185809</v>
+        <v>0.05791962189536486</v>
       </c>
       <c r="AC4">
-        <v>-0.05174723649630953</v>
+        <v>-0.05616530660086067</v>
       </c>
       <c r="AD4">
-        <v>438.1</v>
+        <v>82304</v>
       </c>
       <c r="AE4">
-        <v>11.93632672774285</v>
+        <v>1343.363117851047</v>
       </c>
       <c r="AF4">
-        <v>450.0363267277429</v>
+        <v>83647.36311785104</v>
       </c>
       <c r="AG4">
-        <v>287.9363267277429</v>
+        <v>10085.36311785104</v>
       </c>
       <c r="AH4">
-        <v>0.6096101078126891</v>
+        <v>0.5285317012760095</v>
       </c>
       <c r="AI4">
-        <v>0.6168799417382445</v>
+        <v>0.5850760356604155</v>
       </c>
       <c r="AJ4">
-        <v>0.499771171110009</v>
+        <v>0.119069245474184</v>
       </c>
       <c r="AK4">
-        <v>0.5074337210453136</v>
+        <v>0.145308912105454</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -946,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>210.625</v>
+        <v>218.3129973474801</v>
       </c>
       <c r="AP4">
-        <v>138.4309263114149</v>
+        <v>26.75162630729719</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bancorp (NYSE:USB)</t>
+          <t>JPMorgan Chase &amp; Co. (NYSE:JPM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,13 +981,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0367</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E5">
-        <v>-0.0447</v>
+        <v>0.0898</v>
       </c>
       <c r="F5">
-        <v>0.01</v>
+        <v>0.0167</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,91 +996,91 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.003384296672504541</v>
+        <v>3.106740031582511E-05</v>
       </c>
       <c r="J5">
-        <v>0.002685186291836434</v>
+        <v>2.420018711876903E-05</v>
       </c>
       <c r="K5">
-        <v>5507</v>
+        <v>53773</v>
       </c>
       <c r="L5">
-        <v>0.2238799902431092</v>
+        <v>0.3316291289439278</v>
       </c>
       <c r="M5">
-        <v>2994</v>
+        <v>29754.38</v>
       </c>
       <c r="N5">
-        <v>0.04442960489705064</v>
+        <v>0.04408936123993928</v>
       </c>
       <c r="O5">
-        <v>0.543671690575631</v>
+        <v>0.5533330853774199</v>
       </c>
       <c r="P5">
-        <v>2935</v>
+        <v>12950.38</v>
       </c>
       <c r="Q5">
-        <v>0.04355407160081617</v>
+        <v>0.01918957753495401</v>
       </c>
       <c r="R5">
-        <v>0.5329580533865989</v>
+        <v>0.2408342476707641</v>
       </c>
       <c r="S5">
-        <v>59</v>
+        <v>16804</v>
       </c>
       <c r="T5">
-        <v>0.0197060788243153</v>
+        <v>0.5647571886895308</v>
       </c>
       <c r="U5">
-        <v>64354</v>
+        <v>409160</v>
       </c>
       <c r="V5">
-        <v>0.9549842329808941</v>
+        <v>0.6062839502934881</v>
       </c>
       <c r="W5">
-        <v>0.1352905048519838</v>
+        <v>0.1854452403204503</v>
       </c>
       <c r="X5">
-        <v>0.07180374105306547</v>
+        <v>0.08045948293372115</v>
       </c>
       <c r="Y5">
-        <v>0.06348676379891832</v>
+        <v>0.1049857573867291</v>
       </c>
       <c r="Z5">
-        <v>0.4014442373272118</v>
+        <v>0.3065644284705102</v>
       </c>
       <c r="AA5">
-        <v>0.001077952563007761</v>
+        <v>7.41891653294483E-06</v>
       </c>
       <c r="AB5">
-        <v>0.05367101443463453</v>
+        <v>0.05744679515335324</v>
       </c>
       <c r="AC5">
-        <v>-0.05259306187162677</v>
+        <v>-0.0574393762368203</v>
       </c>
       <c r="AD5">
-        <v>72488</v>
+        <v>920356</v>
       </c>
       <c r="AE5">
-        <v>1428.765352248666</v>
+        <v>8399.812415867947</v>
       </c>
       <c r="AF5">
-        <v>73916.76535224867</v>
+        <v>928755.8124158679</v>
       </c>
       <c r="AG5">
-        <v>9562.765352248665</v>
+        <v>519595.8124158679</v>
       </c>
       <c r="AH5">
-        <v>0.5231035678079931</v>
+        <v>0.579161626911166</v>
       </c>
       <c r="AI5">
-        <v>0.5797631388867447</v>
+        <v>0.7286692126599332</v>
       </c>
       <c r="AJ5">
-        <v>0.1242720256840442</v>
+        <v>0.435004377300283</v>
       </c>
       <c r="AK5">
-        <v>0.1514515273753821</v>
+        <v>0.6003890831854299</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1077,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>196.4444444444445</v>
+        <v>546.2053412462908</v>
       </c>
       <c r="AP5">
-        <v>25.91535325812647</v>
+        <v>308.3654673091204</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVB Financial Group (OTCPK:SIVB.Q)</t>
+          <t>Wells Fargo &amp; Company (NYSE:WFC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,10 +1112,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.252</v>
+        <v>-0.0142</v>
       </c>
       <c r="E6">
-        <v>0.278</v>
+        <v>-0.0447</v>
+      </c>
+      <c r="F6">
+        <v>0.09279999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,88 +1127,91 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.001813922095254842</v>
+        <v>0.001740028730325273</v>
       </c>
       <c r="J6">
-        <v>0.00134373878971687</v>
+        <v>0.001481436269304094</v>
       </c>
       <c r="K6">
-        <v>1672</v>
+        <v>18089</v>
       </c>
       <c r="L6">
-        <v>0.288624201622648</v>
+        <v>0.2322825040128411</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>22871</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.09779640593611484</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>1.264359555530986</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>5073</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.02169215020392246</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.2804466803029466</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>17798</v>
+      </c>
+      <c r="T6">
+        <v>0.7781907218748634</v>
       </c>
       <c r="U6">
-        <v>5258</v>
+        <v>288340</v>
       </c>
       <c r="V6">
-        <v>2682.65306122449</v>
+        <v>1.232941965266904</v>
       </c>
       <c r="W6">
-        <v>0.1328038125496426</v>
+        <v>0.1118704235107857</v>
       </c>
       <c r="X6">
-        <v>136.142554534294</v>
+        <v>0.07975670913964863</v>
       </c>
       <c r="Y6">
-        <v>-136.0097507217444</v>
+        <v>0.03211371437113704</v>
       </c>
       <c r="Z6">
-        <v>0.5414292064502675</v>
+        <v>0.4361853757179426</v>
       </c>
       <c r="AA6">
-        <v>0.0007275394265928476</v>
+        <v>0.0006461808357285933</v>
       </c>
       <c r="AB6">
-        <v>0.05372384849268101</v>
+        <v>0.05843630650270522</v>
       </c>
       <c r="AC6">
-        <v>-0.05299630906608816</v>
+        <v>-0.05779012566697662</v>
       </c>
       <c r="AD6">
-        <v>19268</v>
+        <v>305299</v>
       </c>
       <c r="AE6">
-        <v>372.4597465109435</v>
+        <v>3697.476313129597</v>
       </c>
       <c r="AF6">
-        <v>19640.45974651094</v>
+        <v>308996.4763131296</v>
       </c>
       <c r="AG6">
-        <v>14382.45974651094</v>
+        <v>20656.47631312959</v>
       </c>
       <c r="AH6">
-        <v>0.9999002159598821</v>
+        <v>0.5692011692072373</v>
       </c>
       <c r="AI6">
-        <v>0.5465481695532748</v>
+        <v>0.6254894735991209</v>
       </c>
       <c r="AJ6">
-        <v>0.9998637414623225</v>
+        <v>0.08115859795451273</v>
       </c>
       <c r="AK6">
-        <v>0.4688282493190041</v>
+        <v>0.1004362803658855</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1202,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>226.6823529411765</v>
+        <v>348.9131428571429</v>
       </c>
       <c r="AP6">
-        <v>169.2054087824817</v>
+        <v>23.60740150071953</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1234,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Citigroup Inc. (NYSE:C)</t>
+          <t>Bank of America Corporation (NYSE:BAC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1225,10 +1243,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.019</v>
+        <v>0.0194</v>
+      </c>
+      <c r="E7">
+        <v>-0.0315</v>
       </c>
       <c r="F7">
-        <v>0.0791</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1237,91 +1258,91 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.001885516277239551</v>
+        <v>-0.009187371834334213</v>
       </c>
       <c r="J7">
-        <v>0.001422767106774031</v>
+        <v>-0.008584211965985956</v>
       </c>
       <c r="K7">
-        <v>13580</v>
+        <v>23611</v>
       </c>
       <c r="L7">
-        <v>0.1871864145117715</v>
+        <v>0.2495191596389998</v>
       </c>
       <c r="M7">
-        <v>5700.634</v>
+        <v>17899.442</v>
       </c>
       <c r="N7">
-        <v>0.05790379085445316</v>
+        <v>0.05307893201859541</v>
       </c>
       <c r="O7">
-        <v>0.4197815905743741</v>
+        <v>0.7580975816356782</v>
       </c>
       <c r="P7">
-        <v>3942.634</v>
+        <v>7519.441999999999</v>
       </c>
       <c r="Q7">
-        <v>0.0400470289009356</v>
+        <v>0.02229812251889031</v>
       </c>
       <c r="R7">
-        <v>0.2903265095729013</v>
+        <v>0.3184719833975689</v>
       </c>
       <c r="S7">
-        <v>1758</v>
+        <v>10380</v>
       </c>
       <c r="T7">
-        <v>0.3083867513683565</v>
+        <v>0.5799063456838487</v>
       </c>
       <c r="U7">
-        <v>235051</v>
+        <v>288789</v>
       </c>
       <c r="V7">
-        <v>2.387514080737348</v>
+        <v>0.8563737181705524</v>
       </c>
       <c r="W7">
-        <v>0.07562721020243365</v>
+        <v>0.09127952154700832</v>
       </c>
       <c r="X7">
-        <v>0.1442659015959848</v>
+        <v>0.09337281378781889</v>
       </c>
       <c r="Y7">
-        <v>-0.06863869139355119</v>
+        <v>-0.002093292240810576</v>
       </c>
       <c r="Z7">
-        <v>0.1527033614546918</v>
+        <v>0.1669136694645394</v>
       </c>
       <c r="AA7">
-        <v>0.000217261319771561</v>
+        <v>-0.001432822318704123</v>
       </c>
       <c r="AB7">
-        <v>0.05328535116359653</v>
+        <v>0.05680342988978249</v>
       </c>
       <c r="AC7">
-        <v>-0.05306808984382497</v>
+        <v>-0.05823625220848661</v>
       </c>
       <c r="AD7">
-        <v>630457</v>
+        <v>790439</v>
       </c>
       <c r="AE7">
-        <v>2836.047825594125</v>
+        <v>14081.82123597855</v>
       </c>
       <c r="AF7">
-        <v>633293.0478255941</v>
+        <v>804520.8212359785</v>
       </c>
       <c r="AG7">
-        <v>398242.0478255941</v>
+        <v>515731.8212359785</v>
       </c>
       <c r="AH7">
-        <v>0.8654581183403649</v>
+        <v>0.7046420885386068</v>
       </c>
       <c r="AI7">
-        <v>0.7508026337280579</v>
+        <v>0.7306964930735247</v>
       </c>
       <c r="AJ7">
-        <v>0.8017884912596419</v>
+        <v>0.6046413572345122</v>
       </c>
       <c r="AK7">
-        <v>0.65453287114717</v>
+        <v>0.6349470537691473</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1330,10 +1351,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>895.5355113636364</v>
+        <v>405.9779147406266</v>
       </c>
       <c r="AP7">
-        <v>565.6847270249916</v>
+        <v>264.885373002557</v>
       </c>
     </row>
     <row r="8">
@@ -1344,7 +1365,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bank of America Corporation (NYSE:BAC)</t>
+          <t>The PNC Financial Services Group, Inc. (NYSE:PNC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1353,10 +1374,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0236</v>
+        <v>0.0486</v>
       </c>
       <c r="E8">
-        <v>0.05599999999999999</v>
+        <v>-0.0115</v>
+      </c>
+      <c r="F8">
+        <v>0.201</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1365,91 +1389,91 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.0003773423571590488</v>
+        <v>0.002354890861786656</v>
       </c>
       <c r="J8">
-        <v>0.0003475788591400413</v>
+        <v>0.001919059214494163</v>
       </c>
       <c r="K8">
-        <v>30503</v>
+        <v>5143</v>
       </c>
       <c r="L8">
-        <v>0.3152048113090564</v>
+        <v>0.2510740089826206</v>
       </c>
       <c r="M8">
-        <v>11885.33</v>
+        <v>3035</v>
       </c>
       <c r="N8">
-        <v>0.04460532606957862</v>
+        <v>0.03966298874668876</v>
       </c>
       <c r="O8">
-        <v>0.3896446251188408</v>
+        <v>0.5901224965973167</v>
       </c>
       <c r="P8">
-        <v>7122.33</v>
+        <v>2517</v>
       </c>
       <c r="Q8">
-        <v>0.02672991427458404</v>
+        <v>0.03289349017311882</v>
       </c>
       <c r="R8">
-        <v>0.2334960495688949</v>
+        <v>0.4894030721368851</v>
       </c>
       <c r="S8">
-        <v>4763</v>
+        <v>518</v>
       </c>
       <c r="T8">
-        <v>0.4007461298929016</v>
+        <v>0.170675453047776</v>
       </c>
       <c r="U8">
-        <v>345626</v>
+        <v>5702</v>
       </c>
       <c r="V8">
-        <v>1.297125147398026</v>
+        <v>0.07451675842952861</v>
       </c>
       <c r="W8">
-        <v>0.1268896376721161</v>
+        <v>0.1218287338623712</v>
       </c>
       <c r="X8">
-        <v>0.09208629732141724</v>
+        <v>0.07492717864047174</v>
       </c>
       <c r="Y8">
-        <v>0.0348033403506989</v>
+        <v>0.04690155522189945</v>
       </c>
       <c r="Z8">
-        <v>0.1684613164567303</v>
+        <v>0.1916886050338134</v>
       </c>
       <c r="AA8">
-        <v>5.855359218325977e-05</v>
+        <v>0.0003678617838036719</v>
       </c>
       <c r="AB8">
-        <v>0.05316607740271752</v>
+        <v>0.05868543125106364</v>
       </c>
       <c r="AC8">
-        <v>-0.05310752381053426</v>
+        <v>-0.05831756946725997</v>
       </c>
       <c r="AD8">
-        <v>680417</v>
+        <v>70429</v>
       </c>
       <c r="AE8">
-        <v>9807.419127065023</v>
+        <v>1783.812077935811</v>
       </c>
       <c r="AF8">
-        <v>690224.419127065</v>
+        <v>72212.81207793581</v>
       </c>
       <c r="AG8">
-        <v>344598.419127065</v>
+        <v>66510.81207793581</v>
       </c>
       <c r="AH8">
-        <v>0.7214790208043369</v>
+        <v>0.4855213636148115</v>
       </c>
       <c r="AI8">
-        <v>0.706264809464936</v>
+        <v>0.564419175444751</v>
       </c>
       <c r="AJ8">
-        <v>0.5639411919875552</v>
+        <v>0.465011353952888</v>
       </c>
       <c r="AK8">
-        <v>0.5455420628051416</v>
+        <v>0.5441010661529065</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1458,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>340.5490490490491</v>
+        <v>173.8987654320988</v>
       </c>
       <c r="AP8">
-        <v>172.4716812447773</v>
+        <v>164.2242273529279</v>
       </c>
     </row>
     <row r="9">
@@ -1472,7 +1496,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co. (NYSE:JPM)</t>
+          <t>KeyCorp (NYSE:KEY)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1481,10 +1505,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.06759999999999999</v>
+        <v>-0.0412</v>
       </c>
       <c r="E9">
-        <v>0.116</v>
+        <v>-0.389</v>
+      </c>
+      <c r="F9">
+        <v>0.184</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1493,91 +1520,91 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.0001376591069739018</v>
+        <v>0.006786480083137798</v>
       </c>
       <c r="J9">
-        <v>0.0001110690963860868</v>
+        <v>0.006041622513037308</v>
       </c>
       <c r="K9">
-        <v>51253</v>
+        <v>148</v>
       </c>
       <c r="L9">
-        <v>0.3598444158926076</v>
+        <v>0.03050288540807914</v>
       </c>
       <c r="M9">
-        <v>19257.55</v>
+        <v>801</v>
       </c>
       <c r="N9">
-        <v>0.03916042463760306</v>
+        <v>0.04714371475992608</v>
       </c>
       <c r="O9">
-        <v>0.3757350789222094</v>
+        <v>5.412162162162162</v>
       </c>
       <c r="P9">
-        <v>11708.55</v>
+        <v>774</v>
       </c>
       <c r="Q9">
-        <v>0.02380945602584998</v>
+        <v>0.04555460077925442</v>
       </c>
       <c r="R9">
-        <v>0.2284461397381617</v>
+        <v>5.22972972972973</v>
       </c>
       <c r="S9">
-        <v>7549</v>
+        <v>27</v>
       </c>
       <c r="T9">
-        <v>0.3920020978784944</v>
+        <v>0.03370786516853932</v>
       </c>
       <c r="U9">
-        <v>488231</v>
+        <v>1276</v>
       </c>
       <c r="V9">
-        <v>0.9928227256967569</v>
+        <v>0.07510034960507575</v>
       </c>
       <c r="W9">
-        <v>0.2008503801238342</v>
+        <v>0.01363301400147384</v>
       </c>
       <c r="X9">
-        <v>0.07766460929666422</v>
+        <v>0.07771961002369931</v>
       </c>
       <c r="Y9">
-        <v>0.1231857708271699</v>
+        <v>-0.06408659602222548</v>
       </c>
       <c r="Z9">
-        <v>0.5250371138738917</v>
+        <v>0.1316033585680819</v>
       </c>
       <c r="AA9">
-        <v>5.83153978071321e-05</v>
+        <v>0.0007950978139162452</v>
       </c>
       <c r="AB9">
-        <v>0.05377267467703364</v>
+        <v>0.05924701453850971</v>
       </c>
       <c r="AC9">
-        <v>-0.05371435927922651</v>
+        <v>-0.05845191672459346</v>
       </c>
       <c r="AD9">
-        <v>743872</v>
+        <v>19243</v>
       </c>
       <c r="AE9">
-        <v>7761.965378673001</v>
+        <v>500.359993183077</v>
       </c>
       <c r="AF9">
-        <v>751633.965378673</v>
+        <v>19743.35999318308</v>
       </c>
       <c r="AG9">
-        <v>263402.965378673</v>
+        <v>18467.35999318308</v>
       </c>
       <c r="AH9">
-        <v>0.6045016173928075</v>
+        <v>0.5374688706811616</v>
       </c>
       <c r="AI9">
-        <v>0.7031155043441937</v>
+        <v>0.5395044616820504</v>
       </c>
       <c r="AJ9">
-        <v>0.3488025804407671</v>
+        <v>0.5208240969512486</v>
       </c>
       <c r="AK9">
-        <v>0.4535378324111524</v>
+        <v>0.5228679114442455</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1586,10 +1613,10 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>473.2010178117048</v>
+        <v>144.6842105263158</v>
       </c>
       <c r="AP9">
-        <v>167.5591382815986</v>
+        <v>138.8523307758126</v>
       </c>
     </row>
     <row r="10">
@@ -1600,7 +1627,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The PNC Financial Services Group, Inc. (NYSE:PNC)</t>
+          <t>Comerica Incorporated (NYSE:CMA)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1609,13 +1636,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.047</v>
+        <v>-0.00983</v>
       </c>
       <c r="E10">
-        <v>0.00647</v>
+        <v>-0.147</v>
       </c>
       <c r="F10">
-        <v>0.15</v>
+        <v>0.0973</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1624,91 +1651,91 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.001947513039822188</v>
+        <v>-0.0006968255943427847</v>
       </c>
       <c r="J10">
-        <v>0.001625588773784402</v>
+        <v>-0.0005406903989298786</v>
       </c>
       <c r="K10">
-        <v>6242</v>
+        <v>561</v>
       </c>
       <c r="L10">
-        <v>0.2976065605034805</v>
+        <v>0.1774754824422651</v>
       </c>
       <c r="M10">
-        <v>3701</v>
+        <v>389</v>
       </c>
       <c r="N10">
-        <v>0.06000022696654351</v>
+        <v>0.04782277298320671</v>
       </c>
       <c r="O10">
-        <v>0.5929189362383851</v>
+        <v>0.6934046345811051</v>
       </c>
       <c r="P10">
-        <v>2449</v>
+        <v>375</v>
       </c>
       <c r="Q10">
-        <v>0.03970293321833696</v>
+        <v>0.04610164490669027</v>
       </c>
       <c r="R10">
-        <v>0.3923421980134572</v>
+        <v>0.6684491978609626</v>
       </c>
       <c r="S10">
-        <v>1252</v>
+        <v>14</v>
       </c>
       <c r="T10">
-        <v>0.3382869494731154</v>
+        <v>0.03598971722365039</v>
       </c>
       <c r="U10">
-        <v>4782</v>
+        <v>6393</v>
       </c>
       <c r="V10">
-        <v>0.07752528650473145</v>
+        <v>0.7859408423692558</v>
       </c>
       <c r="W10">
-        <v>0.1582496704188216</v>
+        <v>0.1225425950196592</v>
       </c>
       <c r="X10">
-        <v>0.07305166612719399</v>
+        <v>0.07508544929594824</v>
       </c>
       <c r="Y10">
-        <v>0.08519800429162763</v>
+        <v>0.047457145723711</v>
       </c>
       <c r="Z10">
-        <v>0.2287571184173761</v>
+        <v>0.3720130683319882</v>
       </c>
       <c r="AA10">
-        <v>0.0003718650036225557</v>
+        <v>-0.0002011438943235509</v>
       </c>
       <c r="AB10">
-        <v>0.05409094930797988</v>
+        <v>0.05957393505342666</v>
       </c>
       <c r="AC10">
-        <v>-0.05371908430435733</v>
+        <v>-0.05977507894775021</v>
       </c>
       <c r="AD10">
-        <v>71392</v>
+        <v>7416</v>
       </c>
       <c r="AE10">
-        <v>1935.764307513847</v>
+        <v>361.0133285185877</v>
       </c>
       <c r="AF10">
-        <v>73327.76430751385</v>
+        <v>7777.013328518588</v>
       </c>
       <c r="AG10">
-        <v>68545.76430751385</v>
+        <v>1384.013328518588</v>
       </c>
       <c r="AH10">
-        <v>0.5431249157882244</v>
+        <v>0.4887756306163903</v>
       </c>
       <c r="AI10">
-        <v>0.5970890165778454</v>
+        <v>0.5135710548357153</v>
       </c>
       <c r="AJ10">
-        <v>0.5263484763689131</v>
+        <v>0.1454068406275146</v>
       </c>
       <c r="AK10">
-        <v>0.5807645808955729</v>
+        <v>0.158172710892648</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1717,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>166.803738317757</v>
+        <v>105.9428571428571</v>
       </c>
       <c r="AP10">
-        <v>160.1536549240978</v>
+        <v>19.77161897883697</v>
       </c>
     </row>
     <row r="11">
@@ -1731,7 +1758,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company (NYSE:WFC)</t>
+          <t>Fifth Third Bancorp (NasdaqGS:FITB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1740,13 +1767,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0226</v>
+        <v>0.0186</v>
       </c>
       <c r="E11">
-        <v>-0.0397</v>
+        <v>-0.0009</v>
       </c>
       <c r="F11">
-        <v>0.142</v>
+        <v>0.0592</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1755,91 +1782,91 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.001001588391751439</v>
+        <v>-0.002770642650506429</v>
       </c>
       <c r="J11">
-        <v>0.00087850127160366</v>
+        <v>-0.002199896199473866</v>
       </c>
       <c r="K11">
-        <v>18356</v>
+        <v>2224</v>
       </c>
       <c r="L11">
-        <v>0.2399728076138681</v>
+        <v>0.2758278556368597</v>
       </c>
       <c r="M11">
-        <v>14169</v>
+        <v>1277.11</v>
       </c>
       <c r="N11">
-        <v>0.0792674432850926</v>
+        <v>0.04504701840525421</v>
       </c>
       <c r="O11">
-        <v>0.7719001961211593</v>
+        <v>0.574240107913669</v>
       </c>
       <c r="P11">
-        <v>4662</v>
+        <v>952.1099999999999</v>
       </c>
       <c r="Q11">
-        <v>0.02608122101736902</v>
+        <v>0.03358341622399526</v>
       </c>
       <c r="R11">
-        <v>0.2539769012856832</v>
+        <v>0.4281070143884891</v>
       </c>
       <c r="S11">
-        <v>9507</v>
+        <v>325</v>
       </c>
       <c r="T11">
-        <v>0.6709718399322464</v>
+        <v>0.2544808199763529</v>
       </c>
       <c r="U11">
-        <v>287530</v>
+        <v>3215</v>
       </c>
       <c r="V11">
-        <v>1.608565739837862</v>
+        <v>0.1134014800392232</v>
       </c>
       <c r="W11">
-        <v>0.1170827539578257</v>
+        <v>0.1541447186027169</v>
       </c>
       <c r="X11">
-        <v>0.08052504946562736</v>
+        <v>0.07264314301982633</v>
       </c>
       <c r="Y11">
-        <v>0.03655770449219836</v>
+        <v>0.08150157558289062</v>
       </c>
       <c r="Z11">
-        <v>0.4692935425572848</v>
+        <v>0.2354456285884065</v>
       </c>
       <c r="AA11">
-        <v>0.000412274973891961</v>
+        <v>-0.0005179559435143709</v>
       </c>
       <c r="AB11">
-        <v>0.05425019837084542</v>
+        <v>0.05949004016515909</v>
       </c>
       <c r="AC11">
-        <v>-0.05383792339695346</v>
+        <v>-0.06000799610867346</v>
       </c>
       <c r="AD11">
-        <v>306828</v>
+        <v>21116</v>
       </c>
       <c r="AE11">
-        <v>4031.932503690744</v>
+        <v>576.6984584551667</v>
       </c>
       <c r="AF11">
-        <v>310859.9325036908</v>
+        <v>21692.69845845517</v>
       </c>
       <c r="AG11">
-        <v>23329.93250369077</v>
+        <v>18477.69845845517</v>
       </c>
       <c r="AH11">
-        <v>0.6349143599969747</v>
+        <v>0.4334785900746324</v>
       </c>
       <c r="AI11">
-        <v>0.6302497502057299</v>
+        <v>0.5106964346504465</v>
       </c>
       <c r="AJ11">
-        <v>0.1154494314662674</v>
+        <v>0.3945840243340914</v>
       </c>
       <c r="AK11">
-        <v>0.1134156534364048</v>
+        <v>0.4706291165168867</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1848,650 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>347.4835787089468</v>
+        <v>227.0537634408602</v>
       </c>
       <c r="AP11">
-        <v>26.42121461346633</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>First Citizens BancShares, Inc. (NasdaqGS:FCNC.A)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.333</v>
-      </c>
-      <c r="E12">
-        <v>0.983</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>-0.002153025418092073</v>
-      </c>
-      <c r="J12">
-        <v>-0.002052846368781392</v>
-      </c>
-      <c r="K12">
-        <v>11209</v>
-      </c>
-      <c r="L12">
-        <v>1.734870763039777</v>
-      </c>
-      <c r="M12">
-        <v>493</v>
-      </c>
-      <c r="N12">
-        <v>0.02408531968010005</v>
-      </c>
-      <c r="O12">
-        <v>0.04398251405120885</v>
-      </c>
-      <c r="P12">
-        <v>45</v>
-      </c>
-      <c r="Q12">
-        <v>0.002198457171611567</v>
-      </c>
-      <c r="R12">
-        <v>0.004014631100008922</v>
-      </c>
-      <c r="S12">
-        <v>448</v>
-      </c>
-      <c r="T12">
-        <v>0.9087221095334685</v>
-      </c>
-      <c r="U12">
-        <v>791</v>
-      </c>
-      <c r="V12">
-        <v>0.03864399161654998</v>
-      </c>
-      <c r="W12">
-        <v>1.252122430741734</v>
-      </c>
-      <c r="X12">
-        <v>0.08358924604340176</v>
-      </c>
-      <c r="Y12">
-        <v>1.168533184698332</v>
-      </c>
-      <c r="Z12">
-        <v>0.3346705394715251</v>
-      </c>
-      <c r="AA12">
-        <v>-0.00068702720169223</v>
-      </c>
-      <c r="AB12">
-        <v>0.05347088440834787</v>
-      </c>
-      <c r="AC12">
-        <v>-0.0541579116100401</v>
-      </c>
-      <c r="AD12">
-        <v>39906</v>
-      </c>
-      <c r="AE12">
-        <v>309.5534861314644</v>
-      </c>
-      <c r="AF12">
-        <v>40215.55348613147</v>
-      </c>
-      <c r="AG12">
-        <v>39424.55348613147</v>
-      </c>
-      <c r="AH12">
-        <v>0.6626994423756677</v>
-      </c>
-      <c r="AI12">
-        <v>0.6635731339120294</v>
-      </c>
-      <c r="AJ12">
-        <v>0.6582447862229276</v>
-      </c>
-      <c r="AK12">
-        <v>0.6591240812213665</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>831.375</v>
-      </c>
-      <c r="AP12">
-        <v>821.3448642944055</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>KeyCorp (NYSE:KEY)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>-0.0015</v>
-      </c>
-      <c r="E13">
-        <v>-0.0386</v>
-      </c>
-      <c r="F13">
-        <v>0.2</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0.004081099229443008</v>
-      </c>
-      <c r="J13">
-        <v>0.003354647999790089</v>
-      </c>
-      <c r="K13">
-        <v>1296</v>
-      </c>
-      <c r="L13">
-        <v>0.2127729436874077</v>
-      </c>
-      <c r="M13">
-        <v>837</v>
-      </c>
-      <c r="N13">
-        <v>0.06208231655305924</v>
-      </c>
-      <c r="O13">
-        <v>0.6458333333333334</v>
-      </c>
-      <c r="P13">
-        <v>765</v>
-      </c>
-      <c r="Q13">
-        <v>0.05674190222591436</v>
-      </c>
-      <c r="R13">
-        <v>0.5902777777777778</v>
-      </c>
-      <c r="S13">
-        <v>72</v>
-      </c>
-      <c r="T13">
-        <v>0.08602150537634409</v>
-      </c>
-      <c r="U13">
-        <v>766</v>
-      </c>
-      <c r="V13">
-        <v>0.0568160746471247</v>
-      </c>
-      <c r="W13">
-        <v>0.1201112140871177</v>
-      </c>
-      <c r="X13">
-        <v>0.08418076022807956</v>
-      </c>
-      <c r="Y13">
-        <v>0.03593045385903813</v>
-      </c>
-      <c r="Z13">
-        <v>0.1560845952577727</v>
-      </c>
-      <c r="AA13">
-        <v>0.0005236088752795327</v>
-      </c>
-      <c r="AB13">
-        <v>0.05478189409637468</v>
-      </c>
-      <c r="AC13">
-        <v>-0.05425828522109515</v>
-      </c>
-      <c r="AD13">
-        <v>26530</v>
-      </c>
-      <c r="AE13">
-        <v>545.7101229673132</v>
-      </c>
-      <c r="AF13">
-        <v>27075.71012296731</v>
-      </c>
-      <c r="AG13">
-        <v>26309.71012296731</v>
-      </c>
-      <c r="AH13">
-        <v>0.667583137276801</v>
-      </c>
-      <c r="AI13">
-        <v>0.6696652216940708</v>
-      </c>
-      <c r="AJ13">
-        <v>0.6611840487191533</v>
-      </c>
-      <c r="AK13">
-        <v>0.6632859979414163</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>197.9850746268657</v>
-      </c>
-      <c r="AP13">
-        <v>196.3411203206516</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Fifth Third Bancorp (NasdaqGS:FITB)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>0.0387</v>
-      </c>
-      <c r="E14">
-        <v>0.0275</v>
-      </c>
-      <c r="F14">
-        <v>0.173</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>-0.002940934720795005</v>
-      </c>
-      <c r="J14">
-        <v>-0.002311509577599027</v>
-      </c>
-      <c r="K14">
-        <v>2556</v>
-      </c>
-      <c r="L14">
-        <v>0.3105333495322561</v>
-      </c>
-      <c r="M14">
-        <v>1212.54</v>
-      </c>
-      <c r="N14">
-        <v>0.05162314854629752</v>
-      </c>
-      <c r="O14">
-        <v>0.4743896713615023</v>
-      </c>
-      <c r="P14">
-        <v>912.5400000000001</v>
-      </c>
-      <c r="Q14">
-        <v>0.03885083211641541</v>
-      </c>
-      <c r="R14">
-        <v>0.357018779342723</v>
-      </c>
-      <c r="S14">
-        <v>299.9999999999999</v>
-      </c>
-      <c r="T14">
-        <v>0.2474145182839328</v>
-      </c>
-      <c r="U14">
-        <v>2837</v>
-      </c>
-      <c r="V14">
-        <v>0.1207835390385852</v>
-      </c>
-      <c r="W14">
-        <v>0.1748290013679891</v>
-      </c>
-      <c r="X14">
-        <v>0.07162330248824472</v>
-      </c>
-      <c r="Y14">
-        <v>0.1032056988797443</v>
-      </c>
-      <c r="Z14">
-        <v>0.2511899236216307</v>
-      </c>
-      <c r="AA14">
-        <v>-0.0005806279142477672</v>
-      </c>
-      <c r="AB14">
-        <v>0.05473086401552545</v>
-      </c>
-      <c r="AC14">
-        <v>-0.05531149192977321</v>
-      </c>
-      <c r="AD14">
-        <v>24881</v>
-      </c>
-      <c r="AE14">
-        <v>571.0341684343184</v>
-      </c>
-      <c r="AF14">
-        <v>25452.03416843432</v>
-      </c>
-      <c r="AG14">
-        <v>22615.03416843432</v>
-      </c>
-      <c r="AH14">
-        <v>0.5200625333051045</v>
-      </c>
-      <c r="AI14">
-        <v>0.6060580402985993</v>
-      </c>
-      <c r="AJ14">
-        <v>0.4905292551252878</v>
-      </c>
-      <c r="AK14">
-        <v>0.5775176698986121</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>276.4555555555556</v>
-      </c>
-      <c r="AP14">
-        <v>251.278157427048</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Comerica Incorporated (NYSE:CMA)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>0.0243</v>
-      </c>
-      <c r="E15">
-        <v>0.0293</v>
-      </c>
-      <c r="F15">
-        <v>-0.09849999999999999</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>-0.003510019754581721</v>
-      </c>
-      <c r="J15">
-        <v>-0.002734072604674188</v>
-      </c>
-      <c r="K15">
-        <v>1198</v>
-      </c>
-      <c r="L15">
-        <v>0.3220430107526882</v>
-      </c>
-      <c r="M15">
-        <v>377</v>
-      </c>
-      <c r="N15">
-        <v>0.05122421804940352</v>
-      </c>
-      <c r="O15">
-        <v>0.3146911519198665</v>
-      </c>
-      <c r="P15">
-        <v>361</v>
-      </c>
-      <c r="Q15">
-        <v>0.04905024593059594</v>
-      </c>
-      <c r="R15">
-        <v>0.3013355592654424</v>
-      </c>
-      <c r="S15">
-        <v>16</v>
-      </c>
-      <c r="T15">
-        <v>0.04244031830238727</v>
-      </c>
-      <c r="U15">
-        <v>8112</v>
-      </c>
-      <c r="V15">
-        <v>1.102203864235441</v>
-      </c>
-      <c r="W15">
-        <v>0.2562566844919786</v>
-      </c>
-      <c r="X15">
-        <v>0.07958763649873335</v>
-      </c>
-      <c r="Y15">
-        <v>0.1766690479932453</v>
-      </c>
-      <c r="Z15">
-        <v>1.082249077424332</v>
-      </c>
-      <c r="AA15">
-        <v>-0.00295894755401978</v>
-      </c>
-      <c r="AB15">
-        <v>0.05491595607353575</v>
-      </c>
-      <c r="AC15">
-        <v>-0.05787490362755553</v>
-      </c>
-      <c r="AD15">
-        <v>11911</v>
-      </c>
-      <c r="AE15">
-        <v>380.28636743522</v>
-      </c>
-      <c r="AF15">
-        <v>12291.28636743522</v>
-      </c>
-      <c r="AG15">
-        <v>4179.286367435219</v>
-      </c>
-      <c r="AH15">
-        <v>0.6254761766150351</v>
-      </c>
-      <c r="AI15">
-        <v>0.7119899482534806</v>
-      </c>
-      <c r="AJ15">
-        <v>0.3621852055141646</v>
-      </c>
-      <c r="AK15">
-        <v>0.456688404190604</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>189.0634920634921</v>
-      </c>
-      <c r="AP15">
-        <v>66.33787884817808</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Oakworth Capital Inc. (OTCPK:OAKC)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>-0.01315582238825996</v>
-      </c>
-      <c r="J16">
-        <v>-0.009999991184409505</v>
-      </c>
-      <c r="K16">
-        <v>12.8</v>
-      </c>
-      <c r="L16">
-        <v>0.2265486725663717</v>
-      </c>
-      <c r="M16">
-        <v>-0</v>
-      </c>
-      <c r="N16">
-        <v>-0</v>
-      </c>
-      <c r="O16">
-        <v>-0</v>
-      </c>
-      <c r="P16">
-        <v>-0</v>
-      </c>
-      <c r="Q16">
-        <v>-0</v>
-      </c>
-      <c r="R16">
-        <v>-0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>118.3</v>
-      </c>
-      <c r="V16">
-        <v>0.816988950276243</v>
-      </c>
-      <c r="W16">
-        <v>0.128</v>
-      </c>
-      <c r="X16">
-        <v>0.06487623101817613</v>
-      </c>
-      <c r="Y16">
-        <v>0.06312376898182387</v>
-      </c>
-      <c r="Z16">
-        <v>2.151027253595478</v>
-      </c>
-      <c r="AA16">
-        <v>-0.02151025357337937</v>
-      </c>
-      <c r="AB16">
-        <v>0.055730004817606</v>
-      </c>
-      <c r="AC16">
-        <v>-0.07724025839098536</v>
-      </c>
-      <c r="AD16">
-        <v>74.2</v>
-      </c>
-      <c r="AE16">
-        <v>10.76651982468344</v>
-      </c>
-      <c r="AF16">
-        <v>84.96651982468344</v>
-      </c>
-      <c r="AG16">
-        <v>-33.33348017531655</v>
-      </c>
-      <c r="AH16">
-        <v>0.3697950418952014</v>
-      </c>
-      <c r="AI16">
-        <v>0.4320334742305201</v>
-      </c>
-      <c r="AJ16">
-        <v>-0.2990447735135541</v>
-      </c>
-      <c r="AK16">
-        <v>-0.4253535853051542</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>52.62411347517731</v>
-      </c>
-      <c r="AP16">
-        <v>-23.64076608178479</v>
+        <v>198.6849296608083</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0186</v>
+        <v>0.0258</v>
       </c>
       <c r="E2">
-        <v>-0.0447</v>
+        <v>-0.0315</v>
       </c>
       <c r="F2">
-        <v>0.09279999999999999</v>
+        <v>0.09505</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0008316340642067157</v>
+        <v>-0.0008249001876925312</v>
       </c>
       <c r="J2">
-        <v>-0.0006821152868553484</v>
+        <v>-0.0006526417829969559</v>
       </c>
       <c r="K2">
-        <v>117019</v>
+        <v>119624.5</v>
       </c>
       <c r="L2">
-        <v>0.2514299097147916</v>
+        <v>0.2518665044046556</v>
       </c>
       <c r="M2">
-        <v>85726.227</v>
+        <v>86520.227</v>
       </c>
       <c r="N2">
-        <v>0.05413071048721489</v>
+        <v>0.05362574472774531</v>
       </c>
       <c r="O2">
-        <v>0.7325838282672045</v>
+        <v>0.7232651087360866</v>
       </c>
       <c r="P2">
-        <v>37285.227</v>
+        <v>37379.227</v>
       </c>
       <c r="Q2">
-        <v>0.02354327139799454</v>
+        <v>0.02316786437953341</v>
       </c>
       <c r="R2">
-        <v>0.3186254112580008</v>
+        <v>0.3124713332135139</v>
       </c>
       <c r="S2">
-        <v>48441</v>
+        <v>49141</v>
       </c>
       <c r="T2">
-        <v>0.5650662777915095</v>
+        <v>0.5679712329002558</v>
       </c>
       <c r="U2">
-        <v>1359460</v>
+        <v>1360902.3</v>
       </c>
       <c r="V2">
-        <v>0.858413326401839</v>
+        <v>0.8434952365439526</v>
       </c>
       <c r="W2">
-        <v>0.1184105388187021</v>
+        <v>0.1118704235107857</v>
       </c>
       <c r="X2">
-        <v>0.07771961002369931</v>
+        <v>0.07769908855244355</v>
       </c>
       <c r="Y2">
-        <v>0.04069092879500277</v>
+        <v>0.03417133495834213</v>
       </c>
       <c r="Z2">
-        <v>0.2217526126743046</v>
+        <v>0.2199412909897034</v>
       </c>
       <c r="AA2">
-        <v>0.0002197161760174885</v>
+        <v>0.0001173236560085929</v>
       </c>
       <c r="AB2">
-        <v>0.05843630650270522</v>
+        <v>0.05857250075981084</v>
       </c>
       <c r="AC2">
-        <v>-0.05823625220848661</v>
+        <v>-0.05830793524454332</v>
       </c>
       <c r="AD2">
-        <v>2882989</v>
+        <v>2922806.4</v>
       </c>
       <c r="AE2">
-        <v>33500.27068179353</v>
+        <v>33872.05996972472</v>
       </c>
       <c r="AF2">
-        <v>2916489.270681793</v>
+        <v>2956678.459969725</v>
       </c>
       <c r="AG2">
-        <v>1557029.270681793</v>
+        <v>1595776.159969724</v>
       </c>
       <c r="AH2">
-        <v>0.6480830093459902</v>
+        <v>0.6469632964458167</v>
       </c>
       <c r="AI2">
-        <v>0.7089522244340719</v>
+        <v>0.7077810032280174</v>
       </c>
       <c r="AJ2">
-        <v>0.4957557436748592</v>
+        <v>0.4972528473042321</v>
       </c>
       <c r="AK2">
-        <v>0.5652998493525555</v>
+        <v>0.5665834150308589</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>456.6749564390939</v>
+        <v>457.9317847957204</v>
       </c>
       <c r="AP2">
-        <v>246.6385665581805</v>
+        <v>250.0188261081531</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Citigroup Inc. (NYSE:C)</t>
+          <t>FineMark Holdings, Inc. (OTCPK:FNBT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0127</v>
+        <v>0.057</v>
       </c>
       <c r="E3">
-        <v>-0.157</v>
-      </c>
-      <c r="F3">
-        <v>0.258</v>
+        <v>-0.257</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,91 +731,88 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.002551180986686265</v>
+        <v>0.001460502262945997</v>
       </c>
       <c r="J3">
-        <v>0.001863523101126724</v>
+        <v>0.001168057352275914</v>
       </c>
       <c r="K3">
-        <v>7987</v>
+        <v>3.39</v>
       </c>
       <c r="L3">
-        <v>0.1152392220234316</v>
+        <v>0.03964912280701754</v>
       </c>
       <c r="M3">
-        <v>6573.295</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.04937645585651498</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.8229992487792663</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>4066.295</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03054468657911559</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.5091141855515212</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>2507</v>
-      </c>
-      <c r="T3">
-        <v>0.3813916764727584</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>283023</v>
+        <v>447.3</v>
       </c>
       <c r="V3">
-        <v>2.12597679944053</v>
+        <v>1.389993784959602</v>
       </c>
       <c r="W3">
-        <v>0.042035072207486</v>
+        <v>0.01230043541364296</v>
       </c>
       <c r="X3">
-        <v>0.1271511942237079</v>
+        <v>0.09509806318663665</v>
       </c>
       <c r="Y3">
-        <v>-0.08511612201622185</v>
+        <v>-0.08279762777299368</v>
       </c>
       <c r="Z3">
-        <v>0.117903650287267</v>
+        <v>0.1004434035537659</v>
       </c>
       <c r="AA3">
-        <v>0.0002197161760174885</v>
+        <v>0.0001173236560085929</v>
       </c>
       <c r="AB3">
-        <v>0.05637995120573513</v>
+        <v>0.05481561475735524</v>
       </c>
       <c r="AC3">
-        <v>-0.05616023502971765</v>
+        <v>-0.05469829110134665</v>
       </c>
       <c r="AD3">
-        <v>666387</v>
+        <v>801.5</v>
       </c>
       <c r="AE3">
-        <v>2755.913740873742</v>
+        <v>10.42563528259059</v>
       </c>
       <c r="AF3">
-        <v>669142.9137408737</v>
+        <v>811.9256352825906</v>
       </c>
       <c r="AG3">
-        <v>386119.9137408737</v>
+        <v>364.6256352825906</v>
       </c>
       <c r="AH3">
-        <v>0.8340630166192625</v>
+        <v>0.7161570754111168</v>
       </c>
       <c r="AI3">
-        <v>0.7612158415128771</v>
+        <v>0.6963785774259956</v>
       </c>
       <c r="AJ3">
-        <v>0.7436165199595819</v>
+        <v>0.5311946648561282</v>
       </c>
       <c r="AK3">
-        <v>0.6478283848951619</v>
+        <v>0.5073930254926212</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>915.3667582417582</v>
+        <v>362.6696832579186</v>
       </c>
       <c r="AP3">
-        <v>530.3844968968045</v>
+        <v>164.9889752409912</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bancorp (NYSE:USB)</t>
+          <t>Citigroup Inc. (NYSE:C)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,13 +844,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0316</v>
+        <v>0.0127</v>
       </c>
       <c r="E4">
-        <v>-0.0552</v>
+        <v>-0.157</v>
       </c>
       <c r="F4">
-        <v>0.0585</v>
+        <v>0.258</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,91 +859,91 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.004351021264802606</v>
+        <v>0.002551180986686265</v>
       </c>
       <c r="J4">
-        <v>0.003531486161110188</v>
+        <v>0.001863523101126724</v>
       </c>
       <c r="K4">
-        <v>5483</v>
+        <v>7987</v>
       </c>
       <c r="L4">
-        <v>0.2202273366269028</v>
+        <v>0.1152392220234316</v>
       </c>
       <c r="M4">
-        <v>3126</v>
+        <v>6573.295</v>
       </c>
       <c r="N4">
-        <v>0.04189433139943953</v>
+        <v>0.04937645585651498</v>
       </c>
       <c r="O4">
-        <v>0.5701258435163232</v>
+        <v>0.8229992487792663</v>
       </c>
       <c r="P4">
-        <v>3058</v>
+        <v>4066.295</v>
       </c>
       <c r="Q4">
-        <v>0.04098300237347603</v>
+        <v>0.03054468657911559</v>
       </c>
       <c r="R4">
-        <v>0.5577238737917198</v>
+        <v>0.5091141855515212</v>
       </c>
       <c r="S4">
-        <v>68</v>
+        <v>2507</v>
       </c>
       <c r="T4">
-        <v>0.0217530390275112</v>
+        <v>0.3813916764727584</v>
       </c>
       <c r="U4">
-        <v>73562</v>
+        <v>283023</v>
       </c>
       <c r="V4">
-        <v>0.9858703795283336</v>
+        <v>2.12597679944053</v>
       </c>
       <c r="W4">
-        <v>0.1184105388187021</v>
+        <v>0.042035072207486</v>
       </c>
       <c r="X4">
-        <v>0.07719536702552725</v>
+        <v>0.1270988926387999</v>
       </c>
       <c r="Y4">
-        <v>0.04121517179317484</v>
+        <v>-0.08506382043131389</v>
       </c>
       <c r="Z4">
-        <v>0.4967640292133212</v>
+        <v>0.117903650287267</v>
       </c>
       <c r="AA4">
-        <v>0.001754315294504181</v>
+        <v>0.0002197161760174885</v>
       </c>
       <c r="AB4">
-        <v>0.05791962189536486</v>
+        <v>0.05637127243850948</v>
       </c>
       <c r="AC4">
-        <v>-0.05616530660086067</v>
+        <v>-0.05615155626249199</v>
       </c>
       <c r="AD4">
-        <v>82304</v>
+        <v>666387</v>
       </c>
       <c r="AE4">
-        <v>1343.363117851047</v>
+        <v>2755.913740873742</v>
       </c>
       <c r="AF4">
-        <v>83647.36311785104</v>
+        <v>669142.9137408737</v>
       </c>
       <c r="AG4">
-        <v>10085.36311785104</v>
+        <v>386119.9137408737</v>
       </c>
       <c r="AH4">
-        <v>0.5285317012760095</v>
+        <v>0.8340630166192625</v>
       </c>
       <c r="AI4">
-        <v>0.5850760356604155</v>
+        <v>0.7612158415128771</v>
       </c>
       <c r="AJ4">
-        <v>0.119069245474184</v>
+        <v>0.7436165199595819</v>
       </c>
       <c r="AK4">
-        <v>0.145308912105454</v>
+        <v>0.6478283848951619</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -958,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>218.3129973474801</v>
+        <v>915.3667582417582</v>
       </c>
       <c r="AP4">
-        <v>26.75162630729719</v>
+        <v>530.3844968968045</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co. (NYSE:JPM)</t>
+          <t>U.S. Bancorp (NYSE:USB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,13 +975,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.08599999999999999</v>
+        <v>0.0316</v>
       </c>
       <c r="E5">
-        <v>0.0898</v>
+        <v>-0.0552</v>
       </c>
       <c r="F5">
-        <v>0.0167</v>
+        <v>0.0585</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -996,91 +990,91 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>3.106740031582511E-05</v>
+        <v>0.004351021264802606</v>
       </c>
       <c r="J5">
-        <v>2.420018711876903E-05</v>
+        <v>0.003531486161110188</v>
       </c>
       <c r="K5">
-        <v>53773</v>
+        <v>5483</v>
       </c>
       <c r="L5">
-        <v>0.3316291289439278</v>
+        <v>0.2202273366269028</v>
       </c>
       <c r="M5">
-        <v>29754.38</v>
+        <v>3126</v>
       </c>
       <c r="N5">
-        <v>0.04408936123993928</v>
+        <v>0.04189433139943953</v>
       </c>
       <c r="O5">
-        <v>0.5533330853774199</v>
+        <v>0.5701258435163232</v>
       </c>
       <c r="P5">
-        <v>12950.38</v>
+        <v>3058</v>
       </c>
       <c r="Q5">
-        <v>0.01918957753495401</v>
+        <v>0.04098300237347603</v>
       </c>
       <c r="R5">
-        <v>0.2408342476707641</v>
+        <v>0.5577238737917198</v>
       </c>
       <c r="S5">
-        <v>16804</v>
+        <v>68</v>
       </c>
       <c r="T5">
-        <v>0.5647571886895308</v>
+        <v>0.0217530390275112</v>
       </c>
       <c r="U5">
-        <v>409160</v>
+        <v>73562</v>
       </c>
       <c r="V5">
-        <v>0.6062839502934881</v>
+        <v>0.9858703795283336</v>
       </c>
       <c r="W5">
-        <v>0.1854452403204503</v>
+        <v>0.1184105388187021</v>
       </c>
       <c r="X5">
-        <v>0.08045948293372115</v>
+        <v>0.07717518259590858</v>
       </c>
       <c r="Y5">
-        <v>0.1049857573867291</v>
+        <v>0.04123535622279351</v>
       </c>
       <c r="Z5">
-        <v>0.3065644284705102</v>
+        <v>0.4967640292133212</v>
       </c>
       <c r="AA5">
-        <v>7.41891653294483E-06</v>
+        <v>0.001754315294504181</v>
       </c>
       <c r="AB5">
-        <v>0.05744679515335324</v>
+        <v>0.05791010557667182</v>
       </c>
       <c r="AC5">
-        <v>-0.0574393762368203</v>
+        <v>-0.05615579028216764</v>
       </c>
       <c r="AD5">
-        <v>920356</v>
+        <v>82304</v>
       </c>
       <c r="AE5">
-        <v>8399.812415867947</v>
+        <v>1343.363117851047</v>
       </c>
       <c r="AF5">
-        <v>928755.8124158679</v>
+        <v>83647.36311785104</v>
       </c>
       <c r="AG5">
-        <v>519595.8124158679</v>
+        <v>10085.36311785104</v>
       </c>
       <c r="AH5">
-        <v>0.579161626911166</v>
+        <v>0.5285317012760095</v>
       </c>
       <c r="AI5">
-        <v>0.7286692126599332</v>
+        <v>0.5850760356604155</v>
       </c>
       <c r="AJ5">
-        <v>0.435004377300283</v>
+        <v>0.119069245474184</v>
       </c>
       <c r="AK5">
-        <v>0.6003890831854299</v>
+        <v>0.145308912105454</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1089,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>546.2053412462908</v>
+        <v>218.3129973474801</v>
       </c>
       <c r="AP5">
-        <v>308.3654673091204</v>
+        <v>26.75162630729719</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company (NYSE:WFC)</t>
+          <t>JPMorgan Chase &amp; Co. (NYSE:JPM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,13 +1106,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0142</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E6">
-        <v>-0.0447</v>
+        <v>0.0898</v>
       </c>
       <c r="F6">
-        <v>0.09279999999999999</v>
+        <v>0.0167</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1127,91 +1121,91 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.001740028730325273</v>
+        <v>3.106740031582511E-05</v>
       </c>
       <c r="J6">
-        <v>0.001481436269304094</v>
+        <v>2.420018711876903E-05</v>
       </c>
       <c r="K6">
-        <v>18089</v>
+        <v>53773</v>
       </c>
       <c r="L6">
-        <v>0.2322825040128411</v>
+        <v>0.3316291289439278</v>
       </c>
       <c r="M6">
-        <v>22871</v>
+        <v>29754.38</v>
       </c>
       <c r="N6">
-        <v>0.09779640593611484</v>
+        <v>0.04408936123993928</v>
       </c>
       <c r="O6">
-        <v>1.264359555530986</v>
+        <v>0.5533330853774199</v>
       </c>
       <c r="P6">
-        <v>5073</v>
+        <v>12950.38</v>
       </c>
       <c r="Q6">
-        <v>0.02169215020392246</v>
+        <v>0.01918957753495401</v>
       </c>
       <c r="R6">
-        <v>0.2804466803029466</v>
+        <v>0.2408342476707641</v>
       </c>
       <c r="S6">
-        <v>17798</v>
+        <v>16804</v>
       </c>
       <c r="T6">
-        <v>0.7781907218748634</v>
+        <v>0.5647571886895308</v>
       </c>
       <c r="U6">
-        <v>288340</v>
+        <v>409160</v>
       </c>
       <c r="V6">
-        <v>1.232941965266904</v>
+        <v>0.6062839502934881</v>
       </c>
       <c r="W6">
-        <v>0.1118704235107857</v>
+        <v>0.1854452403204503</v>
       </c>
       <c r="X6">
-        <v>0.07975670913964863</v>
+        <v>0.08043719996778781</v>
       </c>
       <c r="Y6">
-        <v>0.03211371437113704</v>
+        <v>0.1050080403526625</v>
       </c>
       <c r="Z6">
-        <v>0.4361853757179426</v>
+        <v>0.3065644284705102</v>
       </c>
       <c r="AA6">
-        <v>0.0006461808357285933</v>
+        <v>7.41891653294483E-06</v>
       </c>
       <c r="AB6">
-        <v>0.05843630650270522</v>
+        <v>0.05743741762622226</v>
       </c>
       <c r="AC6">
-        <v>-0.05779012566697662</v>
+        <v>-0.05742999870968932</v>
       </c>
       <c r="AD6">
-        <v>305299</v>
+        <v>920356</v>
       </c>
       <c r="AE6">
-        <v>3697.476313129597</v>
+        <v>8399.812415867947</v>
       </c>
       <c r="AF6">
-        <v>308996.4763131296</v>
+        <v>928755.8124158679</v>
       </c>
       <c r="AG6">
-        <v>20656.47631312959</v>
+        <v>519595.8124158679</v>
       </c>
       <c r="AH6">
-        <v>0.5692011692072373</v>
+        <v>0.579161626911166</v>
       </c>
       <c r="AI6">
-        <v>0.6254894735991209</v>
+        <v>0.7286692126599332</v>
       </c>
       <c r="AJ6">
-        <v>0.08115859795451273</v>
+        <v>0.435004377300283</v>
       </c>
       <c r="AK6">
-        <v>0.1004362803658855</v>
+        <v>0.6003890831854299</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1220,10 +1214,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>348.9131428571429</v>
+        <v>546.2053412462908</v>
       </c>
       <c r="AP6">
-        <v>23.60740150071953</v>
+        <v>308.3654673091204</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bank of America Corporation (NYSE:BAC)</t>
+          <t>Wells Fargo &amp; Company (NYSE:WFC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1243,13 +1237,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0194</v>
+        <v>-0.0142</v>
       </c>
       <c r="E7">
-        <v>-0.0315</v>
+        <v>-0.0447</v>
       </c>
       <c r="F7">
-        <v>0.09029999999999999</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1258,91 +1252,91 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-0.009187371834334213</v>
+        <v>0.001740028730325273</v>
       </c>
       <c r="J7">
-        <v>-0.008584211965985956</v>
+        <v>0.001481436269304094</v>
       </c>
       <c r="K7">
-        <v>23611</v>
+        <v>18089</v>
       </c>
       <c r="L7">
-        <v>0.2495191596389998</v>
+        <v>0.2322825040128411</v>
       </c>
       <c r="M7">
-        <v>17899.442</v>
+        <v>22871</v>
       </c>
       <c r="N7">
-        <v>0.05307893201859541</v>
+        <v>0.09779640593611484</v>
       </c>
       <c r="O7">
-        <v>0.7580975816356782</v>
+        <v>1.264359555530986</v>
       </c>
       <c r="P7">
-        <v>7519.441999999999</v>
+        <v>5073</v>
       </c>
       <c r="Q7">
-        <v>0.02229812251889031</v>
+        <v>0.02169215020392246</v>
       </c>
       <c r="R7">
-        <v>0.3184719833975689</v>
+        <v>0.2804466803029466</v>
       </c>
       <c r="S7">
-        <v>10380</v>
+        <v>17798</v>
       </c>
       <c r="T7">
-        <v>0.5799063456838487</v>
+        <v>0.7781907218748634</v>
       </c>
       <c r="U7">
-        <v>288789</v>
+        <v>288340</v>
       </c>
       <c r="V7">
-        <v>0.8563737181705524</v>
+        <v>1.232941965266904</v>
       </c>
       <c r="W7">
-        <v>0.09127952154700832</v>
+        <v>0.1118704235107857</v>
       </c>
       <c r="X7">
-        <v>0.09337281378781889</v>
+        <v>0.07973487799478088</v>
       </c>
       <c r="Y7">
-        <v>-0.002093292240810576</v>
+        <v>0.0321355455160048</v>
       </c>
       <c r="Z7">
-        <v>0.1669136694645394</v>
+        <v>0.4361853757179426</v>
       </c>
       <c r="AA7">
-        <v>-0.001432822318704123</v>
+        <v>0.0006461808357285933</v>
       </c>
       <c r="AB7">
-        <v>0.05680342988978249</v>
+        <v>0.05842690167102133</v>
       </c>
       <c r="AC7">
-        <v>-0.05823625220848661</v>
+        <v>-0.05778072083529273</v>
       </c>
       <c r="AD7">
-        <v>790439</v>
+        <v>305299</v>
       </c>
       <c r="AE7">
-        <v>14081.82123597855</v>
+        <v>3697.476313129597</v>
       </c>
       <c r="AF7">
-        <v>804520.8212359785</v>
+        <v>308996.4763131296</v>
       </c>
       <c r="AG7">
-        <v>515731.8212359785</v>
+        <v>20656.47631312959</v>
       </c>
       <c r="AH7">
-        <v>0.7046420885386068</v>
+        <v>0.5692011692072373</v>
       </c>
       <c r="AI7">
-        <v>0.7306964930735247</v>
+        <v>0.6254894735991209</v>
       </c>
       <c r="AJ7">
-        <v>0.6046413572345122</v>
+        <v>0.08115859795451273</v>
       </c>
       <c r="AK7">
-        <v>0.6349470537691473</v>
+        <v>0.1004362803658855</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1351,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>405.9779147406266</v>
+        <v>348.9131428571429</v>
       </c>
       <c r="AP7">
-        <v>264.885373002557</v>
+        <v>23.60740150071953</v>
       </c>
     </row>
     <row r="8">
@@ -1365,7 +1359,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The PNC Financial Services Group, Inc. (NYSE:PNC)</t>
+          <t>Bank of America Corporation (NYSE:BAC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1374,13 +1368,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0486</v>
+        <v>0.0194</v>
       </c>
       <c r="E8">
-        <v>-0.0115</v>
+        <v>-0.0315</v>
       </c>
       <c r="F8">
-        <v>0.201</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1389,91 +1383,91 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.002354890861786656</v>
+        <v>-0.009187371834334213</v>
       </c>
       <c r="J8">
-        <v>0.001919059214494163</v>
+        <v>-0.008584211965985956</v>
       </c>
       <c r="K8">
-        <v>5143</v>
+        <v>23611</v>
       </c>
       <c r="L8">
-        <v>0.2510740089826206</v>
+        <v>0.2495191596389998</v>
       </c>
       <c r="M8">
-        <v>3035</v>
+        <v>17899.442</v>
       </c>
       <c r="N8">
-        <v>0.03966298874668876</v>
+        <v>0.05307893201859541</v>
       </c>
       <c r="O8">
-        <v>0.5901224965973167</v>
+        <v>0.7580975816356782</v>
       </c>
       <c r="P8">
-        <v>2517</v>
+        <v>7519.441999999999</v>
       </c>
       <c r="Q8">
-        <v>0.03289349017311882</v>
+        <v>0.02229812251889031</v>
       </c>
       <c r="R8">
-        <v>0.4894030721368851</v>
+        <v>0.3184719833975689</v>
       </c>
       <c r="S8">
-        <v>518</v>
+        <v>10380</v>
       </c>
       <c r="T8">
-        <v>0.170675453047776</v>
+        <v>0.5799063456838487</v>
       </c>
       <c r="U8">
-        <v>5702</v>
+        <v>288789</v>
       </c>
       <c r="V8">
-        <v>0.07451675842952861</v>
+        <v>0.8563737181705524</v>
       </c>
       <c r="W8">
-        <v>0.1218287338623712</v>
+        <v>0.09127952154700832</v>
       </c>
       <c r="X8">
-        <v>0.07492717864047174</v>
+        <v>0.09334222869827746</v>
       </c>
       <c r="Y8">
-        <v>0.04690155522189945</v>
+        <v>-0.002062707151269147</v>
       </c>
       <c r="Z8">
-        <v>0.1916886050338134</v>
+        <v>0.1669136694645394</v>
       </c>
       <c r="AA8">
-        <v>0.0003678617838036719</v>
+        <v>-0.001432822318704123</v>
       </c>
       <c r="AB8">
-        <v>0.05868543125106364</v>
+        <v>0.05679439634161366</v>
       </c>
       <c r="AC8">
-        <v>-0.05831756946725997</v>
+        <v>-0.05822721866031779</v>
       </c>
       <c r="AD8">
-        <v>70429</v>
+        <v>790439</v>
       </c>
       <c r="AE8">
-        <v>1783.812077935811</v>
+        <v>14081.82123597855</v>
       </c>
       <c r="AF8">
-        <v>72212.81207793581</v>
+        <v>804520.8212359785</v>
       </c>
       <c r="AG8">
-        <v>66510.81207793581</v>
+        <v>515731.8212359785</v>
       </c>
       <c r="AH8">
-        <v>0.4855213636148115</v>
+        <v>0.7046420885386068</v>
       </c>
       <c r="AI8">
-        <v>0.564419175444751</v>
+        <v>0.7306964930735247</v>
       </c>
       <c r="AJ8">
-        <v>0.465011353952888</v>
+        <v>0.6046413572345122</v>
       </c>
       <c r="AK8">
-        <v>0.5441010661529065</v>
+        <v>0.6349470537691473</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1482,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>173.8987654320988</v>
+        <v>405.9779147406266</v>
       </c>
       <c r="AP8">
-        <v>164.2242273529279</v>
+        <v>264.885373002557</v>
       </c>
     </row>
     <row r="9">
@@ -1496,7 +1490,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KeyCorp (NYSE:KEY)</t>
+          <t>The PNC Financial Services Group, Inc. (NYSE:PNC)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1505,13 +1499,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0412</v>
+        <v>0.0486</v>
       </c>
       <c r="E9">
-        <v>-0.389</v>
+        <v>-0.0115</v>
       </c>
       <c r="F9">
-        <v>0.184</v>
+        <v>0.201</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1520,91 +1514,91 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.006786480083137798</v>
+        <v>0.002354890861786656</v>
       </c>
       <c r="J9">
-        <v>0.006041622513037308</v>
+        <v>0.001919059214494163</v>
       </c>
       <c r="K9">
-        <v>148</v>
+        <v>5143</v>
       </c>
       <c r="L9">
-        <v>0.03050288540807914</v>
+        <v>0.2510740089826206</v>
       </c>
       <c r="M9">
-        <v>801</v>
+        <v>3035</v>
       </c>
       <c r="N9">
-        <v>0.04714371475992608</v>
+        <v>0.03966298874668876</v>
       </c>
       <c r="O9">
-        <v>5.412162162162162</v>
+        <v>0.5901224965973167</v>
       </c>
       <c r="P9">
-        <v>774</v>
+        <v>2517</v>
       </c>
       <c r="Q9">
-        <v>0.04555460077925442</v>
+        <v>0.03289349017311882</v>
       </c>
       <c r="R9">
-        <v>5.22972972972973</v>
+        <v>0.4894030721368851</v>
       </c>
       <c r="S9">
-        <v>27</v>
+        <v>518</v>
       </c>
       <c r="T9">
-        <v>0.03370786516853932</v>
+        <v>0.170675453047776</v>
       </c>
       <c r="U9">
-        <v>1276</v>
+        <v>5702</v>
       </c>
       <c r="V9">
-        <v>0.07510034960507575</v>
+        <v>0.07451675842952861</v>
       </c>
       <c r="W9">
-        <v>0.01363301400147384</v>
+        <v>0.1218287338623712</v>
       </c>
       <c r="X9">
-        <v>0.07771961002369931</v>
+        <v>0.07490845245431885</v>
       </c>
       <c r="Y9">
-        <v>-0.06408659602222548</v>
+        <v>0.04692028140805235</v>
       </c>
       <c r="Z9">
-        <v>0.1316033585680819</v>
+        <v>0.1916886050338134</v>
       </c>
       <c r="AA9">
-        <v>0.0007950978139162452</v>
+        <v>0.0003678617838036719</v>
       </c>
       <c r="AB9">
-        <v>0.05924701453850971</v>
+        <v>0.05867579702834699</v>
       </c>
       <c r="AC9">
-        <v>-0.05845191672459346</v>
+        <v>-0.05830793524454332</v>
       </c>
       <c r="AD9">
-        <v>19243</v>
+        <v>70429</v>
       </c>
       <c r="AE9">
-        <v>500.359993183077</v>
+        <v>1783.812077935811</v>
       </c>
       <c r="AF9">
-        <v>19743.35999318308</v>
+        <v>72212.81207793581</v>
       </c>
       <c r="AG9">
-        <v>18467.35999318308</v>
+        <v>66510.81207793581</v>
       </c>
       <c r="AH9">
-        <v>0.5374688706811616</v>
+        <v>0.4855213636148115</v>
       </c>
       <c r="AI9">
-        <v>0.5395044616820504</v>
+        <v>0.564419175444751</v>
       </c>
       <c r="AJ9">
-        <v>0.5208240969512486</v>
+        <v>0.465011353952888</v>
       </c>
       <c r="AK9">
-        <v>0.5228679114442455</v>
+        <v>0.5441010661529065</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1613,10 +1607,10 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>144.6842105263158</v>
+        <v>173.8987654320988</v>
       </c>
       <c r="AP9">
-        <v>138.8523307758126</v>
+        <v>164.2242273529279</v>
       </c>
     </row>
     <row r="10">
@@ -1627,7 +1621,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Comerica Incorporated (NYSE:CMA)</t>
+          <t>CIB Marine Bancshares, Inc. (OTCPK:CIBH)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1636,13 +1630,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.00983</v>
+        <v>0.0258</v>
       </c>
       <c r="E10">
-        <v>-0.147</v>
-      </c>
-      <c r="F10">
-        <v>0.0973</v>
+        <v>0.042</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1651,91 +1642,88 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>-0.0006968255943427847</v>
+        <v>0.001961548066006877</v>
       </c>
       <c r="J10">
-        <v>-0.0005406903989298786</v>
+        <v>0.001173527311165964</v>
       </c>
       <c r="K10">
-        <v>561</v>
+        <v>4.15</v>
       </c>
       <c r="L10">
-        <v>0.1774754824422651</v>
+        <v>0.1217008797653959</v>
       </c>
       <c r="M10">
-        <v>389</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.04782277298320671</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.6934046345811051</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>375</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.04610164490669027</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.6684491978609626</v>
+        <v>-0</v>
       </c>
       <c r="S10">
-        <v>14</v>
-      </c>
-      <c r="T10">
-        <v>0.03598971722365039</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>6393</v>
+        <v>13.8</v>
       </c>
       <c r="V10">
-        <v>0.7859408423692558</v>
+        <v>0.3689839572192514</v>
       </c>
       <c r="W10">
-        <v>0.1225425950196592</v>
+        <v>0.05971223021582734</v>
       </c>
       <c r="X10">
-        <v>0.07508544929594824</v>
+        <v>0.07550339508564062</v>
       </c>
       <c r="Y10">
-        <v>0.047457145723711</v>
+        <v>-0.01579116486981328</v>
       </c>
       <c r="Z10">
-        <v>0.3720130683319882</v>
+        <v>0.1578911622572933</v>
       </c>
       <c r="AA10">
-        <v>-0.0002011438943235509</v>
+        <v>0.0001852895911006704</v>
       </c>
       <c r="AB10">
-        <v>0.05957393505342666</v>
+        <v>0.05857250075981084</v>
       </c>
       <c r="AC10">
-        <v>-0.05977507894775021</v>
+        <v>-0.05838721116871017</v>
       </c>
       <c r="AD10">
-        <v>7416</v>
+        <v>33.6</v>
       </c>
       <c r="AE10">
-        <v>361.0133285185877</v>
+        <v>3.435556054745827</v>
       </c>
       <c r="AF10">
-        <v>7777.013328518588</v>
+        <v>37.03555605474583</v>
       </c>
       <c r="AG10">
-        <v>1384.013328518588</v>
+        <v>23.23555605474582</v>
       </c>
       <c r="AH10">
-        <v>0.4887756306163903</v>
+        <v>0.497551949870663</v>
       </c>
       <c r="AI10">
-        <v>0.5135710548357153</v>
+        <v>0.2861312392329147</v>
       </c>
       <c r="AJ10">
-        <v>0.1454068406275146</v>
+        <v>0.3832001809922748</v>
       </c>
       <c r="AK10">
-        <v>0.158172710892648</v>
+        <v>0.2009378157332967</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1744,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>105.9428571428571</v>
+        <v>44.56233421750663</v>
       </c>
       <c r="AP10">
-        <v>19.77161897883697</v>
+        <v>30.8163873405117</v>
       </c>
     </row>
     <row r="11">
@@ -1758,127 +1746,645 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>KeyCorp (NYSE:KEY)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>-0.0412</v>
+      </c>
+      <c r="E11">
+        <v>-0.389</v>
+      </c>
+      <c r="F11">
+        <v>0.184</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0.006786480083137798</v>
+      </c>
+      <c r="J11">
+        <v>0.006041622513037308</v>
+      </c>
+      <c r="K11">
+        <v>148</v>
+      </c>
+      <c r="L11">
+        <v>0.03050288540807914</v>
+      </c>
+      <c r="M11">
+        <v>801</v>
+      </c>
+      <c r="N11">
+        <v>0.04714371475992608</v>
+      </c>
+      <c r="O11">
+        <v>5.412162162162162</v>
+      </c>
+      <c r="P11">
+        <v>774</v>
+      </c>
+      <c r="Q11">
+        <v>0.04555460077925442</v>
+      </c>
+      <c r="R11">
+        <v>5.22972972972973</v>
+      </c>
+      <c r="S11">
+        <v>27</v>
+      </c>
+      <c r="T11">
+        <v>0.03370786516853932</v>
+      </c>
+      <c r="U11">
+        <v>1276</v>
+      </c>
+      <c r="V11">
+        <v>0.07510034960507575</v>
+      </c>
+      <c r="W11">
+        <v>0.01363301400147384</v>
+      </c>
+      <c r="X11">
+        <v>0.07769908855244355</v>
+      </c>
+      <c r="Y11">
+        <v>-0.06406607455096971</v>
+      </c>
+      <c r="Z11">
+        <v>0.1316033585680819</v>
+      </c>
+      <c r="AA11">
+        <v>0.0007950978139162452</v>
+      </c>
+      <c r="AB11">
+        <v>0.05923752271923451</v>
+      </c>
+      <c r="AC11">
+        <v>-0.05844242490531826</v>
+      </c>
+      <c r="AD11">
+        <v>19243</v>
+      </c>
+      <c r="AE11">
+        <v>500.359993183077</v>
+      </c>
+      <c r="AF11">
+        <v>19743.35999318308</v>
+      </c>
+      <c r="AG11">
+        <v>18467.35999318308</v>
+      </c>
+      <c r="AH11">
+        <v>0.5374688706811616</v>
+      </c>
+      <c r="AI11">
+        <v>0.5395044616820504</v>
+      </c>
+      <c r="AJ11">
+        <v>0.5208240969512486</v>
+      </c>
+      <c r="AK11">
+        <v>0.5228679114442455</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>144.6842105263158</v>
+      </c>
+      <c r="AP11">
+        <v>138.8523307758126</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>First Citizens BancShares, Inc. (NasdaqGS:FCNC.A)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.413</v>
+      </c>
+      <c r="E12">
+        <v>0.422</v>
+      </c>
+      <c r="F12">
+        <v>0.134</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>-0.0004406107996512921</v>
+      </c>
+      <c r="J12">
+        <v>-0.0003198718357793494</v>
+      </c>
+      <c r="K12">
+        <v>2591</v>
+      </c>
+      <c r="L12">
+        <v>0.2766979923109782</v>
+      </c>
+      <c r="M12">
+        <v>794</v>
+      </c>
+      <c r="N12">
+        <v>0.0271878702378425</v>
+      </c>
+      <c r="O12">
+        <v>0.306445387881127</v>
+      </c>
+      <c r="P12">
+        <v>94</v>
+      </c>
+      <c r="Q12">
+        <v>0.003218715116318886</v>
+      </c>
+      <c r="R12">
+        <v>0.03627942879197221</v>
+      </c>
+      <c r="S12">
+        <v>700</v>
+      </c>
+      <c r="T12">
+        <v>0.8816120906801007</v>
+      </c>
+      <c r="U12">
+        <v>862</v>
+      </c>
+      <c r="V12">
+        <v>0.02951630244964765</v>
+      </c>
+      <c r="W12">
+        <v>0.1328173057207299</v>
+      </c>
+      <c r="X12">
+        <v>0.08003122812249136</v>
+      </c>
+      <c r="Y12">
+        <v>0.05278607759823858</v>
+      </c>
+      <c r="Z12">
+        <v>0.1573685520495569</v>
+      </c>
+      <c r="AA12">
+        <v>-5.033776763802985E-05</v>
+      </c>
+      <c r="AB12">
+        <v>0.05899597463888336</v>
+      </c>
+      <c r="AC12">
+        <v>-0.05904631240652138</v>
+      </c>
+      <c r="AD12">
+        <v>38918</v>
+      </c>
+      <c r="AE12">
+        <v>345.6293976396735</v>
+      </c>
+      <c r="AF12">
+        <v>39263.62939763967</v>
+      </c>
+      <c r="AG12">
+        <v>38401.62939763967</v>
+      </c>
+      <c r="AH12">
+        <v>0.5734609924554324</v>
+      </c>
+      <c r="AI12">
+        <v>0.6323497994583506</v>
+      </c>
+      <c r="AJ12">
+        <v>0.5680224581192757</v>
+      </c>
+      <c r="AK12">
+        <v>0.6271739642298081</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>598.7384615384616</v>
+      </c>
+      <c r="AP12">
+        <v>590.7942984252257</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Comerica Incorporated (NYSE:CMA)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>-0.00983</v>
+      </c>
+      <c r="E13">
+        <v>-0.147</v>
+      </c>
+      <c r="F13">
+        <v>0.0973</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>-0.0006968255943427847</v>
+      </c>
+      <c r="J13">
+        <v>-0.0005406903989298786</v>
+      </c>
+      <c r="K13">
+        <v>561</v>
+      </c>
+      <c r="L13">
+        <v>0.1774754824422651</v>
+      </c>
+      <c r="M13">
+        <v>389</v>
+      </c>
+      <c r="N13">
+        <v>0.04782277298320671</v>
+      </c>
+      <c r="O13">
+        <v>0.6934046345811051</v>
+      </c>
+      <c r="P13">
+        <v>375</v>
+      </c>
+      <c r="Q13">
+        <v>0.04610164490669027</v>
+      </c>
+      <c r="R13">
+        <v>0.6684491978609626</v>
+      </c>
+      <c r="S13">
+        <v>14</v>
+      </c>
+      <c r="T13">
+        <v>0.03598971722365039</v>
+      </c>
+      <c r="U13">
+        <v>6393</v>
+      </c>
+      <c r="V13">
+        <v>0.7859408423692558</v>
+      </c>
+      <c r="W13">
+        <v>0.1225425950196592</v>
+      </c>
+      <c r="X13">
+        <v>0.07506662135583581</v>
+      </c>
+      <c r="Y13">
+        <v>0.04747597366382343</v>
+      </c>
+      <c r="Z13">
+        <v>0.3720130683319882</v>
+      </c>
+      <c r="AA13">
+        <v>-0.0002011438943235509</v>
+      </c>
+      <c r="AB13">
+        <v>0.05956430975161589</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05976545364593944</v>
+      </c>
+      <c r="AD13">
+        <v>7416</v>
+      </c>
+      <c r="AE13">
+        <v>361.0133285185877</v>
+      </c>
+      <c r="AF13">
+        <v>7777.013328518588</v>
+      </c>
+      <c r="AG13">
+        <v>1384.013328518588</v>
+      </c>
+      <c r="AH13">
+        <v>0.4887756306163903</v>
+      </c>
+      <c r="AI13">
+        <v>0.5135710548357153</v>
+      </c>
+      <c r="AJ13">
+        <v>0.1454068406275146</v>
+      </c>
+      <c r="AK13">
+        <v>0.158172710892648</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>105.9428571428571</v>
+      </c>
+      <c r="AP13">
+        <v>19.77161897883697</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Fifth Third Bancorp (NasdaqGS:FITB)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D11">
+      <c r="D14">
         <v>0.0186</v>
       </c>
-      <c r="E11">
+      <c r="E14">
         <v>-0.0009</v>
       </c>
-      <c r="F11">
+      <c r="F14">
         <v>0.0592</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>-0.002770642650506429</v>
       </c>
-      <c r="J11">
+      <c r="J14">
         <v>-0.002199896199473866</v>
       </c>
-      <c r="K11">
+      <c r="K14">
         <v>2224</v>
       </c>
-      <c r="L11">
+      <c r="L14">
         <v>0.2758278556368597</v>
       </c>
-      <c r="M11">
+      <c r="M14">
         <v>1277.11</v>
       </c>
-      <c r="N11">
+      <c r="N14">
         <v>0.04504701840525421</v>
       </c>
-      <c r="O11">
+      <c r="O14">
         <v>0.574240107913669</v>
       </c>
-      <c r="P11">
+      <c r="P14">
         <v>952.1099999999999</v>
       </c>
-      <c r="Q11">
+      <c r="Q14">
         <v>0.03358341622399526</v>
       </c>
-      <c r="R11">
+      <c r="R14">
         <v>0.4281070143884891</v>
       </c>
-      <c r="S11">
+      <c r="S14">
         <v>325</v>
       </c>
-      <c r="T11">
+      <c r="T14">
         <v>0.2544808199763529</v>
       </c>
-      <c r="U11">
+      <c r="U14">
         <v>3215</v>
       </c>
-      <c r="V11">
+      <c r="V14">
         <v>0.1134014800392232</v>
       </c>
-      <c r="W11">
+      <c r="W14">
         <v>0.1541447186027169</v>
       </c>
-      <c r="X11">
-        <v>0.07264314301982633</v>
-      </c>
-      <c r="Y11">
-        <v>0.08150157558289062</v>
-      </c>
-      <c r="Z11">
+      <c r="X14">
+        <v>0.07262588526550268</v>
+      </c>
+      <c r="Y14">
+        <v>0.08151883333721427</v>
+      </c>
+      <c r="Z14">
         <v>0.2354456285884065</v>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <v>-0.0005179559435143709</v>
       </c>
-      <c r="AB11">
-        <v>0.05949004016515909</v>
-      </c>
-      <c r="AC11">
-        <v>-0.06000799610867346</v>
-      </c>
-      <c r="AD11">
+      <c r="AB14">
+        <v>0.05948026327784751</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05999821922136189</v>
+      </c>
+      <c r="AD14">
         <v>21116</v>
       </c>
-      <c r="AE11">
+      <c r="AE14">
         <v>576.6984584551667</v>
       </c>
-      <c r="AF11">
+      <c r="AF14">
         <v>21692.69845845517</v>
       </c>
-      <c r="AG11">
+      <c r="AG14">
         <v>18477.69845845517</v>
       </c>
-      <c r="AH11">
+      <c r="AH14">
         <v>0.4334785900746324</v>
       </c>
-      <c r="AI11">
+      <c r="AI14">
         <v>0.5106964346504465</v>
       </c>
-      <c r="AJ11">
+      <c r="AJ14">
         <v>0.3945840243340914</v>
       </c>
-      <c r="AK11">
+      <c r="AK14">
         <v>0.4706291165168867</v>
       </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
         <v>227.0537634408602</v>
       </c>
-      <c r="AP11">
+      <c r="AP14">
         <v>198.6849296608083</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Oakworth Capital Inc. (OTCPK:OAKC)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.132</v>
+      </c>
+      <c r="E15">
+        <v>-0.0265</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>-0.01470109909626265</v>
+      </c>
+      <c r="J15">
+        <v>-0.01145796749271983</v>
+      </c>
+      <c r="K15">
+        <v>6.96</v>
+      </c>
+      <c r="L15">
+        <v>0.1279411764705882</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>119.2</v>
+      </c>
+      <c r="V15">
+        <v>0.7655748233782916</v>
+      </c>
+      <c r="W15">
+        <v>0.06230975828111011</v>
+      </c>
+      <c r="X15">
+        <v>0.06913352121375416</v>
+      </c>
+      <c r="Y15">
+        <v>-0.006823762932644042</v>
+      </c>
+      <c r="Z15">
+        <v>0.6808621505989072</v>
+      </c>
+      <c r="AA15">
+        <v>-0.007801296388585589</v>
+      </c>
+      <c r="AB15">
+        <v>0.06001333780546005</v>
+      </c>
+      <c r="AC15">
+        <v>-0.06781463419404564</v>
+      </c>
+      <c r="AD15">
+        <v>64.3</v>
+      </c>
+      <c r="AE15">
+        <v>12.29869895418344</v>
+      </c>
+      <c r="AF15">
+        <v>76.59869895418343</v>
+      </c>
+      <c r="AG15">
+        <v>-42.60130104581657</v>
+      </c>
+      <c r="AH15">
+        <v>0.3297422641583159</v>
+      </c>
+      <c r="AI15">
+        <v>0.3784545026720894</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.3766736614987451</v>
+      </c>
+      <c r="AK15">
+        <v>-0.5120428754454035</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>38.73493975903614</v>
+      </c>
+      <c r="AP15">
+        <v>-25.66343436494974</v>
       </c>
     </row>
   </sheetData>
